--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E1F6F9-7AA7-46B4-B17C-46B9358F3C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91198F5-38D1-472A-9647-E7BAE46F40A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
-    <sheet name="ArchIntro" sheetId="5" r:id="rId1"/>
-    <sheet name="Architecture" sheetId="1" r:id="rId2"/>
-    <sheet name="Adaptive" sheetId="2" r:id="rId3"/>
-    <sheet name="Agency" sheetId="4" r:id="rId4"/>
+    <sheet name="Start" sheetId="7" r:id="rId1"/>
+    <sheet name="ArchIntro" sheetId="5" r:id="rId2"/>
+    <sheet name="Architecture" sheetId="1" r:id="rId3"/>
+    <sheet name="Adaptive" sheetId="2" r:id="rId4"/>
+    <sheet name="Agency" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="98">
   <si>
     <t>Index</t>
   </si>
@@ -142,9 +143,6 @@
   </si>
   <si>
     <t>Positioned between **practice, research and policy...**</t>
-  </si>
-  <si>
-    <t>AAA000/AAA00_.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">The renovated façade is animated by its new inhabitants; a rich biodiversity of deep soil, people opening up their apartments outside and natural integration of solar power production. A new language for the city of Barcelona marking an important entrance to the historical city and a park. 
@@ -353,6 +351,47 @@
 I projektet Generative Care fick AAA första pris för en strategi som återanvänder Växjö sjukhus. I projektet Could You Live Here? samarbetar AAA med Riksbyggen i Stockholm för att undersöka alternativ för återbruk av en kontors- och verkstadsbyggnad genom en process med generativ AI.
 Varje byggnad och plats är unik – metoderna måste anpassas efter dess specifika behov och potential. **Att navigera i skärningspunkten mellan ekonomi och ekologi, kultur och teknik är AAA:s expertis.**</t>
   </si>
+  <si>
+    <t>AAA000/AAA00.jpg</t>
+  </si>
+  <si>
+    <t>More</t>
+  </si>
+  <si>
+    <t>Less</t>
+  </si>
+  <si>
+    <t>In embracing the complexity of an existing building or place – we can do more* – with less**.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;ast;   
+More culture  
+More patina  
+More diversity  
+More value  
+More history  
+More memories  
+More attachment  
+More craftmanship  
+...  
+More fun </t>
+  </si>
+  <si>
+    <t>&amp;ast;&amp;ast;   
+Less costs  
+Less co₂  
+Less disturbance  
+Less resources  
+Less pollution  
+Less standardisation  
+Less monotony  
+Less something  
+...  
+Less destruction</t>
+  </si>
+  <si>
+    <t>svsv</t>
+  </si>
 </sst>
 </file>
 
@@ -401,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -410,7 +449,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,15 +782,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD8EFA5-DFD4-4477-B3EC-CBF24932B9A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC864E3-E602-4CEC-9B03-25CC71D1A1B8}">
   <dimension ref="A1:H258"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="4"/>
-    <col min="2" max="5" width="40.6328125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="47.6328125" style="4" customWidth="1"/>
-    <col min="7" max="8" width="10.6328125" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="4"/>
+    <col min="2" max="5" width="40.6328125" customWidth="1"/>
+    <col min="6" max="6" width="47.6328125" customWidth="1"/>
+    <col min="7" max="8" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -781,17 +817,2647 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A145" s="2"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A147" s="2"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A155" s="2"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A157" s="2"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A178" s="2"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A179" s="2"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A180" s="2"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A182" s="2"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="2"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A183" s="2"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A184" s="2"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A185" s="2"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="2"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A186" s="2"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+      <c r="H186" s="2"/>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A187" s="2"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="2"/>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A188" s="2"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="2"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A189" s="2"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="2"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A190" s="2"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="2"/>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A191" s="2"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="2"/>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A192" s="2"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A193" s="2"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+      <c r="H193" s="2"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A194" s="2"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+      <c r="H194" s="2"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A195" s="2"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
+      <c r="H195" s="2"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A196" s="2"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A197" s="2"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A198" s="2"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+      <c r="H198" s="2"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A199" s="2"/>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A200" s="2"/>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A201" s="2"/>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A202" s="2"/>
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="2"/>
+      <c r="H202" s="2"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A203" s="2"/>
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+      <c r="H203" s="2"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A204" s="2"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+      <c r="H204" s="2"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A205" s="2"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+      <c r="H205" s="2"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A206" s="2"/>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+      <c r="H206" s="2"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+      <c r="H207" s="2"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A208" s="2"/>
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+      <c r="F208" s="2"/>
+      <c r="G208" s="2"/>
+      <c r="H208" s="2"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A209" s="2"/>
+      <c r="B209" s="2"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
+      <c r="E209" s="2"/>
+      <c r="F209" s="2"/>
+      <c r="G209" s="2"/>
+      <c r="H209" s="2"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A210" s="2"/>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+      <c r="E210" s="2"/>
+      <c r="F210" s="2"/>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A211" s="2"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+      <c r="E211" s="2"/>
+      <c r="F211" s="2"/>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A212" s="2"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A213" s="2"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A214" s="2"/>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="2"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A225" s="2"/>
+      <c r="B225" s="2"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
+      <c r="E225" s="2"/>
+      <c r="F225" s="2"/>
+      <c r="G225" s="2"/>
+      <c r="H225" s="2"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A226" s="2"/>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+      <c r="F226" s="2"/>
+      <c r="G226" s="2"/>
+      <c r="H226" s="2"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A227" s="2"/>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+      <c r="F227" s="2"/>
+      <c r="G227" s="2"/>
+      <c r="H227" s="2"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A228" s="2"/>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
+      <c r="E228" s="2"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="2"/>
+      <c r="H228" s="2"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A229" s="2"/>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
+      <c r="E229" s="2"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="2"/>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A230" s="2"/>
+      <c r="B230" s="2"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2"/>
+      <c r="H230" s="2"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A231" s="2"/>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+      <c r="H231" s="2"/>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A232" s="2"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+      <c r="H232" s="2"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A233" s="2"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="2"/>
+      <c r="H233" s="2"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A234" s="2"/>
+      <c r="B234" s="2"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+      <c r="H234" s="2"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A235" s="2"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+      <c r="H235" s="2"/>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A236" s="2"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2"/>
+      <c r="H236" s="2"/>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="2"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="2"/>
+      <c r="H237" s="2"/>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A238" s="2"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="2"/>
+      <c r="H238" s="2"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="2"/>
+      <c r="H240" s="2"/>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+      <c r="F241" s="2"/>
+      <c r="G241" s="2"/>
+      <c r="H241" s="2"/>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A242" s="2"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="2"/>
+      <c r="H242" s="2"/>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A243" s="2"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="2"/>
+      <c r="H243" s="2"/>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A244" s="2"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="2"/>
+      <c r="H244" s="2"/>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="2"/>
+      <c r="H245" s="2"/>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A246" s="2"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="2"/>
+      <c r="H246" s="2"/>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="2"/>
+      <c r="H247" s="2"/>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+      <c r="H248" s="2"/>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
+      <c r="H249" s="2"/>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="2"/>
+      <c r="H250" s="2"/>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="2"/>
+      <c r="H251" s="2"/>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="2"/>
+      <c r="H252" s="2"/>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A253" s="2"/>
+      <c r="B253" s="2"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="2"/>
+      <c r="H253" s="2"/>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A254" s="2"/>
+      <c r="B254" s="2"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="2"/>
+      <c r="H254" s="2"/>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A255" s="2"/>
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="2"/>
+      <c r="F255" s="2"/>
+      <c r="G255" s="2"/>
+      <c r="H255" s="2"/>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="2"/>
+      <c r="H256" s="2"/>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A257" s="2"/>
+      <c r="B257" s="2"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
+      <c r="E257" s="2"/>
+      <c r="F257" s="2"/>
+      <c r="G257" s="2"/>
+      <c r="H257" s="2"/>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A258" s="2"/>
+      <c r="B258" s="2"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="2"/>
+      <c r="H258" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD8EFA5-DFD4-4477-B3EC-CBF24932B9A8}">
+  <dimension ref="A1:H258"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="5" width="40.6328125" customWidth="1"/>
+    <col min="6" max="6" width="47.6328125" customWidth="1"/>
+    <col min="7" max="8" width="10.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -3363,7 +6029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753E04D3-4F26-42C1-99ED-EFD612322389}">
   <dimension ref="A1:H268"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3410,10 +6076,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>20</v>
@@ -3436,10 +6102,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>21</v>
@@ -3453,22 +6119,22 @@
     </row>
     <row r="4" spans="1:8" ht="145" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2">
         <v>0.15</v>
@@ -3479,22 +6145,22 @@
     </row>
     <row r="5" spans="1:8" ht="174" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" s="2">
         <v>0.15</v>
@@ -3505,22 +6171,22 @@
     </row>
     <row r="6" spans="1:8" ht="174" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2">
         <v>0.15</v>
@@ -3531,22 +6197,22 @@
     </row>
     <row r="7" spans="1:8" ht="203" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2">
         <v>0.15</v>
@@ -3557,22 +6223,22 @@
     </row>
     <row r="8" spans="1:8" ht="145" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2">
         <v>0.15</v>
@@ -3583,22 +6249,22 @@
     </row>
     <row r="9" spans="1:8" ht="174" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9" s="2">
         <v>0.15</v>
@@ -3609,22 +6275,22 @@
     </row>
     <row r="10" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -6219,7 +8885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5497F668-57EF-48E2-B618-0ACF80820C95}">
   <dimension ref="A1:G268"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6260,10 +8926,10 @@
         <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -6275,13 +8941,13 @@
         <v>25</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>23</v>
@@ -6298,16 +8964,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -6321,16 +8987,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -8708,7 +11374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04093925-E5E8-4C20-AF94-7ABD304FA7F3}">
   <dimension ref="A1:G268"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8746,10 +11412,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>22</v>
@@ -8766,7 +11432,7 @@
         <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -8779,13 +11445,13 @@
         <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91198F5-38D1-472A-9647-E7BAE46F40A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93778B2-94A6-4697-9903-ED6869869172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -93,20 +93,6 @@
     <t>Prio</t>
   </si>
   <si>
-    <t>As a society, we are witnessing rapid changes in how we plan, build and live. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources. Unlike generations before us, we are given the chance to pass on the embodied social and cultural heritage.
-We are building for a new future, with the beautiful legacy before us.</t>
-  </si>
-  <si>
-    <t>The richness inherited is often irreplaceable. Materials and elaborate craftmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
-Qualities we so often try to recreate in new projects are already present, waiting to be cared for, adapted and brought into new use.
-Both research and practice show that the most sustainable and resource sufficient building is an existing one that is taken care of and developed through time.</t>
-  </si>
-  <si>
-    <t>The starting point is observation and evaluation. AAA believes the concrete reality – the materials, structure and layers of use – must be understood to unlock the hidden potential of a building or place.
-Through early-stage mapping of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. This iterative process builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
-It is not a phase of design, but an iterative process of exploring scenarios to find the best way forward.</t>
-  </si>
-  <si>
     <t>AAA019/AAA019_Generative_Care_01.jpg, AAA019/AAA019_Generative_Care_02.jpg, AAA019/AAA019_Generative_Care_03.jpg, AAA019/AAA019_Generative_Care_05.jpg, AAA019/AAA019_Generative_Care_04.jpg</t>
   </si>
   <si>
@@ -114,9 +100,6 @@
   </si>
   <si>
     <t>AAA019/AAA019_Generative_Care_06.gif</t>
-  </si>
-  <si>
-    <t>AAA000/AAA01.jpg</t>
   </si>
   <si>
     <t>Part three</t>
@@ -128,21 +111,10 @@
     <t>**How do we identify and develop value?**</t>
   </si>
   <si>
-    <t>**Breaking new ground**</t>
-  </si>
-  <si>
-    <t>AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places. This approach helps property owners and municipalities to understand the existing potential early, before large investments are made or decisions narrow down the possible options.
-AAA has extensive experience in **leading architecture projects** for a renovation or addition. While much of AAA’s work focuses on early-stage strategies, the agency also takes on selected design commissions where a similar approach is applied.
-Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
-  </si>
-  <si>
     <t>plus</t>
   </si>
   <si>
     <t>TitleSv</t>
-  </si>
-  <si>
-    <t>Positioned between **practice, research and policy...**</t>
   </si>
   <si>
     <t xml:space="preserve">The renovated façade is animated by its new inhabitants; a rich biodiversity of deep soil, people opening up their apartments outside and natural integration of solar power production. A new language for the city of Barcelona marking an important entrance to the historical city and a park. 
@@ -165,10 +137,6 @@
     <t>Charlottenborg</t>
   </si>
   <si>
-    <t xml:space="preserve">Entering the courtyard all visitors are struck by the vivid activity in the space, a constantly changing landscape full of impressions. Built from reusable materials, the structure creates an open framework that gives space to what is already there to grow. The sound from the courtyard is recorded, delayed one day and then replayed in the interior acoustically separated room, offering a sort of collective memory. 
-Meeting pavilion 15 sqm, Art Fair Charlottenborg Copenhagen, competition 2023 /MA. </t>
-  </si>
-  <si>
     <t>AAA012/AAA012_Casa_Mangabeira_00.jpg, AAA012/AAA012_Casa_Mangabeira_01.jpg, AAA012/AAA012_Casa_Mangabeira_02.jpg, AAA012/AAA012_Casa_Mangabeira_03.jpg, AAA012/AAA012_Casa_Mangabeira_04.jpg</t>
   </si>
   <si>
@@ -182,10 +150,6 @@
   </si>
   <si>
     <t>Brunnsparken</t>
-  </si>
-  <si>
-    <t>The small kiosk reacts differently to all of its sides, activating the public space by opening the shutters. I.e., offering a pause for the passer-by, protection for a short standing coffee, calmness for a seated meal or a quick take-a-away. The simple and economical wooden structure is built off site and lifted in place. The versatile design allows the building to adapted to many different uses, prolonging its longevity. 
-Public kiosk 18 sqm, Gothenburg, competition 2022 /MG MA.</t>
   </si>
   <si>
     <t>AAA007/AAA007_Sofielund_01.jpg, AAA007/AAA007_Sofielund_02.jpg</t>
@@ -210,10 +174,6 @@
     <t>Vacant Potential</t>
   </si>
   <si>
-    <t>The way we work and live in the city is changing. Some buildings are having a hard time to adapt, especially offices from the 80s. What are their potential? How can we find new uses with simple interventions? Combining sustainability and economy, this research explores how current trends of renovation and demolition can evolve.
-Grant funded research on renovations, 2023-ongoing.</t>
-  </si>
-  <si>
     <t>AAA018/AAA018_Trondheim_02.jpg, AAA018/AAA018_Trondheim_01.jpg, AAA018/AAA018_Trondheim_04.jpg, AAA018/AAA018_Trondheim_03.jpg</t>
   </si>
   <si>
@@ -226,10 +186,6 @@
     <t>Kyrkan mitt i byn</t>
   </si>
   <si>
-    <t>The new church, surrounded by greenery, is a central part of Trondheim’s east. A large square in front creates space for activities and highlights the building. Its design combines a timeless main space with adaptable rooms. A green landscape wall creates a calm courtyard while reused materials, optimised space and design integrated solar panels ensures the building's longevity.
-Church in Trondheim 1’400 sqm, competition 2023 /MG.</t>
-  </si>
-  <si>
     <t>AAAvisualdiary/AAAvisualdiary000.jpg</t>
   </si>
   <si>
@@ -239,86 +195,14 @@
     <t>Visual Diary</t>
   </si>
   <si>
-    <t xml:space="preserve">Seeing the qualities of what is already there, how can the architecture be inspired by the everyday spaces that surround us. Photos ongoing investigating of atmospheres and possibilities of existing spaces. </t>
-  </si>
-  <si>
-    <t>... Henrik has been invited to talk or be part of numerous conferences, discussions and presentations. Recently at xxx, xxx
-As a specialised practice, AAA often ventures into **collaborations** and has over the years worked with Riksbyggen, MOD Group, xxx, xxx
-AAA’s work and reflections have been **featured in** xxx, xxx
-AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB.
-© 2025 Agency for Adaptive Architecture. All rights reserved.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centrally located in Växjö, the brief asked, what happens with the whole built environement if the hospital moves? We proposed a first phase with three interventions that helps the city to understand how the existing structures can be reused, at the same time, mediating what citizens are expecting. The second phase is a hypothesis of what could be learnt from the site and how that would take form.
-Development strategy för Växjö municipality, competition 2023–ongoing /MA OC LG. </t>
-  </si>
-  <si>
-    <t>Centralt i Växjö ställde uppdraget frågan: vad händer om vi börjar i det som redan finns? Inom sjukhusområdet prövas en framtid för vårdens arkitektur där de befintliga byggnaderna återbrukas och byggs på. Förslaget introducerar en ny typologi med delade utrymmen och dagsljus, där sjukhusparken flätas samman med vårdmiljöerna. Arbetet kombinerar strategisk utveckling med konkreta rumsliga grepp för att lära av platsen och låta det ta form.
-Utvecklingsstrategi för Växjö kommun, tävling 2023–pågående /MA OC LG.</t>
-  </si>
-  <si>
     <t>Den renoverade fasaden levandegörs av sina nya invånare: balkonger, skuggspel och öppningar artikulerar vardagens rytm. Små men precisa tillägg förstärker byggnadens relation till gatan och skapar ett generöst mellanrum mellan privat och offentligt. Ett nytt språk för Barcelona som markerar ett viktigt steg i samtalet om den befintliga stadens arkitektur.
 Internationell tävling 2024 organiserad av Fundació Mies van der Rohe, UIA, UNESCO.</t>
-  </si>
-  <si>
-    <t>Väggar flyttas, tas bort och läggs till – planens logik skärps samtidigt som nya rumsliga sekvenser uppstår. Nya öppningar tas upp mot utsidan och binder samman inne och ute. Ett rum för meditation ger huset en stilla tyngdpunkt och gör hemmet flexibelt i vardagen.</t>
-  </si>
-  <si>
-    <t>När man stiger in på gården möts man av ljus, höjd och en robust materialitet. Exponeringarna ordnas av enkla, tydliga strukturer som ger ett öppet ramverk åt det som redan finns på plats – konsten, institutionen och publiken. Greppen är lågmälda men precisa och förstärker byggnadens egna kvaliteter.</t>
-  </si>
-  <si>
-    <t>Den lilla kiosken svarar olika beroende på sammanhang – lä för kaffe i farten, lugn för en sittande måltid eller snabb take-away. Genom att arbeta med skalan i detalj blir den ett vardagsrum i staden, ett enkelt tillskott som gör platsen mer användbar och trivsam.</t>
-  </si>
-  <si>
-    <t>Hur vi arbetar och lever i staden förändras. Många byggnader står delvis eller helt tomma. Vilka värden kan låsas upp med små, precisa ingrepp? Här prövas strategier som kombinerar hållbarhet och ekonomi – att göra lite men rätt, i rätt tid, för att skapa mycket.</t>
-  </si>
-  <si>
-    <t>Den nya kyrkan, omsluten av stadens kvarter, samlar dagsljuset i en stilla volym. En tidlös huvudsal kompletteras med anpassningsbara rum för vardagens verksamhet. Ett grönt landskap binder byggnaden till gaturummet och gör platsen till en öppen resurs för fler.</t>
-  </si>
-  <si>
-    <t>Att se kvaliteterna i det som redan finns – en pågående studie och undersökning av stämningar och möjligheter i befintliga miljöer.</t>
-  </si>
-  <si>
-    <t>Uppgiften är att samverka med det som redan fungerar och låta det växa. Projektet utvecklar en *aktiv form* – en form som svarar direkt på platsens förhållanden. Genom ett tydligt protokoll uttrycks en ny balans mellan sociala, rumsliga och ekonomiska värden och driver området stegvis framåt.</t>
   </si>
   <si>
     <t>**Vad kan en befintlig byggnad eller plats erbjuda?**</t>
   </si>
   <si>
-    <t>Som samhälle står vi inför snabba förändringar i hur vi planerar, bygger och lever. En byggnad kan stå i över hundra år, medan användningen kan skifta på några månader. Att ta hand om den miljö och de byggnader vi redan har utmanar oss att vara kreativa och att använda våra ekonomiska och ekologiska resurser klokt. Till skillnad från generationer före oss har vi möjligheten att föra vidare det inbäddade sociala och kulturella arvet.
-Vi bygger för en ny framtid, med det vackra arvet framför oss.</t>
-  </si>
-  <si>
-    <t>Rikedomarna vi ärver är ofta oersättliga. Material och hantverk från tidigare tider, spår av mänsklig närvaro och berättelser, sociala vävar som ger sammanhang och tillhörighet, en arkitektur med karaktär och lång livslängd.
-Kvaliteter som vi ofta försöker återskapa i nya projekt finns redan här — de väntar bara på att tas om hand, anpassas och ges nytt liv.
-Forskning och praktik visar att den mest hållbara byggnaden är den som redan finns, som vårdas och utvecklas över tid.</t>
-  </si>
-  <si>
     <t>**Hur identifierar och utvecklar vi värde?**</t>
-  </si>
-  <si>
-    <t>Utgångspunkten är att se och förstå. AAA menar att den konkreta verkligheten – material, struktur och brukslager – måste uppfattas för att frigöra en byggnads eller plats dolda potential.
-Genom tidig kartläggning av material, struktur och rumslig logik kan olika alternativ för återbruk eller ombyggnad prövas. Denna iterativa process skapar en grund för välgrundade beslut där miljömässiga, sociala och arkitektoniska kvaliteter integreras från början.
-Det är inte en designfas, utan en process av utforskande scenarier för att hitta den mest hållbara vägen framåt.</t>
-  </si>
-  <si>
-    <t>**Att bryta ny mark**</t>
-  </si>
-  <si>
-    <t>AAA är en framväxande **Agency for Adaptive Architecture**, verksam inom strategi och gestaltning av den befintliga miljön.
-Varje byggnad, varje situation rymmer en **dold potential**. AAA:s roll som arkitekter är att känna igen och lyfta fram dessa värden. Oavsett om det gäller en enskild byggnad eller ett helt område kan små, precisa justeringar få stor effekt och förändra hur en plats upplevs och används. AAA:s arbetssätt bygger på att lyssna, lära och utforma strategier som samspelar med miljön och de behov som finns på platsen.</t>
-  </si>
-  <si>
-    <t>AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga skeden** för befintliga byggnader och platser. Det gör det möjligt för fastighetsägare och kommuner att förstå potentialen innan stora investeringar görs eller besluten begränsar handlingsutrymmet.
-AAA har även **omfattande erfarenhet av att leda arkitekturprojekt** för ombyggnad och tillbyggnad. Även om mycket av arbetet handlar om strategi och process, tar byrån också på sig utvalda uppdrag där samma förhållningssätt tillämpas i byggnadsskala.
-Grundat av **Henrik Almquist** (MArch D’État Française, Arkitekt SAR/MSA) med erfarenhet från Stockholm, Paris och Tokyo. Han har arbetat med allt från dialoger på plats till tidiga designförslag och genomförande. Henrik undervisar vid Lunds universitet där han leder masterstudion _Act of Altering_ och är en aktiv röst i samtalet om den befintliga miljön och hållbarhet.</t>
-  </si>
-  <si>
-    <t>...Henrik har bjudits in att tala och delta i ett flertal konferenser, samtal och presentationer – senast vid xxx, xxx.
-Som specialiserad praktik samarbetar AAA regelbundet med andra aktörer och har under åren arbetat med Riksbyggen, MOD Group, xxx, xxx.
-AAA:s arbete och reflektioner har **uppmärksammats i** xxx, xxx.
-AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB.
-© 2025 Agency for Adaptive Architecture. All rights reserved.</t>
   </si>
   <si>
     <t>Positionerad mellan **praktik, forskning och policy**...</t>
@@ -342,16 +226,6 @@
     <t>AAA000/AAA03.png</t>
   </si>
   <si>
-    <t>AAA has long worked with these challenges, developing methods that combine design intelligence, strategic decision-making and architectural experience.
-In the project Generative Care AAA received first prize for a reuse strategy of Växjö hospital. In the project Could You Live Here? AAA currently collaborates with the developer Riksbyggen to explore adaptive reuse alternatives of an office and workshop building in Stockholm working with generative AI.
-Each building and place presents its own unique case; methods must be tailored to its specific needs and potential. **Navigating this intersection of economy and ecology, culture and technology, is AAA’s expertise.**</t>
-  </si>
-  <si>
-    <t>AAA har länge arbetat med dessa frågor och utvecklat metoder som förenar arkitektoniskt omdöme, strategiskt beslutsfattande och erfarenhet från praktiskt arbete.
-I projektet Generative Care fick AAA första pris för en strategi som återanvänder Växjö sjukhus. I projektet Could You Live Here? samarbetar AAA med Riksbyggen i Stockholm för att undersöka alternativ för återbruk av en kontors- och verkstadsbyggnad genom en process med generativ AI.
-Varje byggnad och plats är unik – metoderna måste anpassas efter dess specifika behov och potential. **Att navigera i skärningspunkten mellan ekonomi och ekologi, kultur och teknik är AAA:s expertis.**</t>
-  </si>
-  <si>
     <t>AAA000/AAA00.jpg</t>
   </si>
   <si>
@@ -361,20 +235,7 @@
     <t>Less</t>
   </si>
   <si>
-    <t>In embracing the complexity of an existing building or place – we can do more* – with less**.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;ast;   
-More culture  
-More patina  
-More diversity  
-More value  
-More history  
-More memories  
-More attachment  
-More craftmanship  
-...  
-More fun </t>
+    <t>svsv</t>
   </si>
   <si>
     <t>&amp;ast;&amp;ast;   
@@ -383,14 +244,162 @@
 Less disturbance  
 Less resources  
 Less pollution  
-Less standardisation  
 Less monotony  
-Less something  
+Less material   
+Less heavy investment   
 ...  
 Less destruction</t>
   </si>
   <si>
-    <t>svsv</t>
+    <t>&amp;ast;   
+More culture  
+More patina  
+More diversity  
+More value  
+More memories  
+More attachment  
+More craftmanship  
+More beauty   
+...  
+More fun</t>
+  </si>
+  <si>
+    <t>As a society, we are witnessing rapid changes in how we plan, build and live. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources. Unlike generations before us, we are given the chance to pass on an embodied social and cultural heritage.
+We are building for a new future, with the beautiful legacy from before us.</t>
+  </si>
+  <si>
+    <t>**Building your legacy**</t>
+  </si>
+  <si>
+    <t>AAA000/Potential.gif</t>
+  </si>
+  <si>
+    <t>AAA has long worked with these challenges, developing methods that combine design intelligence, strategic decision-making and architectural experience.
+* In Växjö AAA received first prize for a reuse strategy of Växjö hospital. 
+* Together with the property developer Riksbyggen, AAA is currently exploring adaptive reuse alternatives of an office and workshop building in Stockholm working with *generative AI*.
+* Recurrently AAA is invited to speak on the evolving practices and sustainable strategies for urban planning.
+Each building and place presents its own unique case; methods must be tailored to its specific needs and potential. **Navigating this intersection of economy and ecology, culture and technology, is AAA’s expertise.**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How can space and use be inspired by the everyday environments surrounding us? Ongoing photographic exploration of atmospheres and possibilities in existing settings. </t>
+  </si>
+  <si>
+    <t>The richness inherited is often irreplaceable. Materials and elaborate craftmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
+**Qualities we so often try to recreate are already present, waiting to be cared for, adapted and brought into new use.**</t>
+  </si>
+  <si>
+    <t>The starting point is observation and evaluation. AAA believes the concrete reality – the materials, structure and layers of use – must be understood to unlock the hidden potential of a building or place.
+* Through **early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
+* This **iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
+* It is **not a phase of design**, but an iterative process of exploring scenarios of the best way forward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places. This approach helps property owners and municipalities to understand the existing potential early, before large investments are made or decisions narrow down the possible options.
+ * AAA has extensive experience in **leading architecture projects** for a renovation or addition. 
+Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
+  </si>
+  <si>
+    <t>Positioned between **practice, research and policy**...</t>
+  </si>
+  <si>
+    <t>* AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga utvecklingsskeden** för befintliga byggnader och platser. Detta synsätt hjälper fastighetsägare och kommuner att tidigt förstå den befintliga potentialen, innan stora investeringar görs eller beslut begränsar de möjliga alternativen.
+* AAA har lång erfarenhet av **att leda arkitekturprojekt** för renoveringar eller tillägg.
+Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
+  </si>
+  <si>
+    <t>Utgångspunkten är observation och utvärdering. AAA anser att den konkreta verkligheten – materialen, strukturen och användningslagren – måste förstås för att frigöra den dolda potentialen i en byggnad eller plats.
+* Genom **tidig kartläggning** av material, struktur och rumslig logik, utvärderas olika alternativ för återanvändning eller anpassning.
+* Denna **iterativa process** bygger en grund för informerade beslutsfattanden, där miljömässiga, sociala och arkitektoniska kvaliteter integreras från start.
+* Det är **inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
+  </si>
+  <si>
+    <t>**Att utveckla ert arv**</t>
+  </si>
+  <si>
+    <t>Centralt i Växjö ställde uppdraget frågan: vad händer om vi börjar i det som redan finns? Inom sjukhusområdet prövas en framtid för vårdens arkitektur där de befintliga byggnaderna återbrukas och byggs på. Förslaget introducerar en ny typologi med delade utrymmen och dagsljus, där sjukhusparken flätas samman med vårdmiljöerna. Arbetet kombinerar strategisk utveckling med konkreta rumsliga grepp för att lära av platsen och låta det ta form.
+Utvecklingsstrategi för Växjö kommun, tävling 2023–pågående med  Morgane Martin-Alonzo, arkitekt stadsplanerare, Oscar Aparicio Chavez, arkitekt, Léa Ganteil, arkitekt återbruk.</t>
+  </si>
+  <si>
+    <t>Centrally located in Växjö, the brief asked, what happens with the whole built environment if the hospital moves? We proposed a first phase with three interventions that helps the city to understand how the existing structures can be reused, at the same time, mediating what citizens are expecting. The second phase is a hypothesis of what could be learnt from the site and how that would take form.
+Development strategy för Växjö municipality, competition 2023–ongoing with Morgane Martin-Alonzo, architect urbanist, Oscar Aparicio Chavez, architect, Léa Ganteil, architect reuse.</t>
+  </si>
+  <si>
+    <t>The new church, surrounded by greenery, is a central part of Trondheim’s east. A large square in front creates space for activities and highlights the building. Its design combines a timeless main space with adaptable rooms. A green landscape wall creates a calm courtyard while reused materials, optimised space and design integrated solar panels ensures the building's longevity.
+Church in Trondheim 1’400 sqm, competition 2023 with Markus Gustafsson, architect engineer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entering the courtyard all visitors are struck by the vivid activity in the space, a constantly changing landscape full of impressions. Built from reusable materials, the structure creates an open framework that gives space to what is already there to grow. The sound from the courtyard is recorded, delayed one day and then replayed in the interior acoustically separated room, offering a sort of collective memory. 
+Meeting pavilion 15 sqm, Art Fair Charlottenborg Copenhagen, competition 2023 with Morgane Martin-Alonzo, architect urbanist. </t>
+  </si>
+  <si>
+    <t>Väggar flyttas, tas bort och läggs till, vilket hittar nya användningsområden och förstärker vilande kvaliteter i byggnaden. Den 70-talsvillan öppnas upp mellan de interna ytorna samtidigt som nya öppningar grävs ut mot utsidan. Ett rum för meditation utökas i bakre delen och erbjuder utsikt över en ny trädgård.
+Renovering privatbostad 300 kvm, Belo Horizonte Brasilien, designförslag 2023.</t>
+  </si>
+  <si>
+    <t>När besökare kommer in på gården slås de av den livliga aktiviteten i rummet, ett ständigt föränderligt landskap fullt av intryck. Strukturen är byggd av återanvändbart material och skapar ett öppet ramverk som ger utrymme för det som redan finns att växa. Ljudet från gården spelas in, fördröjs ett dygn och spelas sedan upp igen i det akustiskt separerade rummet inomhus, vilket erbjuder ett slags kollektivt minne.
+Mötespaviljong 15 kvm, Konstmässa Charlottenborg Köpenhamn, tävling 2023 med Morgane Martin-Alonzo, arkitekt stadsplanerare.</t>
+  </si>
+  <si>
+    <t>Uppgiften ligger i att interagera med det som redan finns och att föreslå en lösning för kontinuitet. Genom att agera på stadens alla skalor, föreslår detta projekt ett designperspektiv med en aktiv form. Genom att definiera ett protokoll uttrycks en ny balans mellan de lokala utrymmenas/praktikernas särart och den marknadsdrivna urbaniseringen, samtidigt som det ges form åt ett mellanliggande utrymme som säkerställer en tidsmässighet i användningen.
+Utvecklingsstrategi för Sofielunds industriområde, Malmö Sverige, MArch vid ENSA Paris Malaquais 2020.</t>
+  </si>
+  <si>
+    <t>Den nya kyrkan, omgiven av grönska, är en central del av Trondheims östra sida. Ett stort torg framför skapar utrymme för aktiviteter och framhäver byggnaden. Dess design kombinerar ett tidlöst huvudutrymme med anpassningsbara rum. En grön landskapsvägg skapar en lugn innergård samtidigt som återanvänt material, optimerat utrymme och designintegrerade solpaneler säkerställer byggnadens livslängd.
+Kyrka i Trondheim 1 400 kvm, tävling 2023 med Markus Gustafsson, arkitekt ingenjör.</t>
+  </si>
+  <si>
+    <t>Hur kan rum och användning inspireras av de vardagliga miljöerna runt omkring oss? Pågående fotografisk utforskning av atmosfärer och möjligheter i den befintliga miljöer.</t>
+  </si>
+  <si>
+    <t>... Henrik has been invited to talk or be part of numerous **conferences, discussions and presentations**. Recently at [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/).
+As a specialised practice, AAA often ventures into **collaborations** and has over the years worked with [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). For [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private clients.
+AAA’s work and reflections have been **featured in** [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
+AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB.
+© 2025 Agency for Adaptive Architecture. All rights reserved.</t>
+  </si>
+  <si>
+    <t>... Henrik har blivit inbjuden att tala eller delta i flertalet **konferenser, diskussioner och presentationer**. Nyligen på [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/).
+Som specialiserad praktik ger sig AAA ofta in i **samarbeten** och har genom åren arbetat med [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). För [Riksbyggen](https://www.riksbyggen.se), [Lunds kommun](https://en.lundcity.se/), [Växjö kommun](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privata klienter.
+AAA:s arbete och reflektioner har **uppmärksammats i** [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
+AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB.
+© 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
+  </si>
+  <si>
+    <t>In embracing the complexity of an existing building or place – we can do more* – with less**</t>
+  </si>
+  <si>
+    <t>Som samhälle ser vi en snabba förändring i hur vi planerar, bygger och lever. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. Till skillnad från generationer före oss, ges vi chansen att föra vidare ett inbyggt socialt och kulturellt arv.
+Vi bygger för en ny framtid, med det vackra arvet från för.</t>
+  </si>
+  <si>
+    <t>Den rikedom som finns i det vi ärvt är oftast oersättlig. Material och genomarbetat hantverk från tidigare tider, lager av mänsklig prägel och berättelser, en tätt vävd social struktur som skapar mening och tillhörighet, design av bestående kvalitet och karaktär, livfullt mångfacetterade användningsområden och en stark känsla för plats.
+**Kvaliteter vi så ofta försöker återskapa är redan närvarande, i väntan på att tas om hand, anpassas och ges en ny användning.**</t>
+  </si>
+  <si>
+    <t>AAA har länge arbetat med dessa utmaningar och utvecklat metoder som kombinerar designintelligens, strategiskt beslutsfattande och arkitektonisk erfarenhet.
+* I Växjö mottog AAA första pris för en återanvändningsstrategi för Växjö sjukhus.
+* Tillsammans med fastighetsutvecklaren Riksbyggen undersöker AAA för närvarande alternativa anpassningar och återanvändningar av en kontors- och verkstadsbyggnad i Stockholm med hjälp av *generativ AI*.
+* AAA bjuds återkommande in för att tala om utvecklingen av praktiken och hållbara strategier för stadsplanering.
+Varje byggnad och plats presenterar sitt unika fall; metoder måste skräddarsys efter dess specifika behov och potential. **Att navigera i denna skärningspunkt mellan ekonomi och ekologi, kultur och teknik, är AAA:s expertis.**</t>
+  </si>
+  <si>
+    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära – för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The kiosk reacts differently to all of its sides, activating the public space by opening the shutters. I.e., offering a pause for the passer-by, protection for a short standing coffee, calmness for a seated meal or a quick take-a-away. The simple and economical wooden structure is built off site and lifted in place. The versatile design allows the building to adapted to many different uses, prolonging its longevity. 
+Public kiosk 18 sqm, Gothenburg, competition 2022 with Markus Gustafsson, architect engineer, Morgane Martin-Alonzo, architect urbanist. </t>
+  </si>
+  <si>
+    <t>Kiosken reagerar olika på alla sina sidor och aktiverar det offentliga rummet genom att öppna luckorna. Den kan till exempel erbjuda en paus för förbipasserande, skydd för en snabb ståfika, lugn för en sittande måltid eller en snabb take-away. Den enkla och ekonomiska träkonstruktionen byggs på annan plats och lyfts på plats. Den mångsidiga designen gör att byggnaden kan anpassas till många olika användningsområden, vilket förlänger dess livslängd.
+Offentlig kiosk 18 kvm, Göteborg, tävling 2022 med Markus Gustafsson, arkitekt ingenjör, Morgane Martin-Alonzo, arkitekt stadsplanerare.</t>
+  </si>
+  <si>
+    <t>The way we work and live in the city is changing. Some buildings are having a hard time to adapt, especially offices from the 80s. What are their potential? How can we find new uses with simple interventions? Combining sustainability and economy, this research explores how current trends of renovation and demolition can evolve.
+Research on renovations, 2023-ongoing.</t>
+  </si>
+  <si>
+    <t>Sättet vi arbetar och lever i staden förändras. Vissa byggnader har svårt att anpassa sig, särskilt kontor från 80-talet. Vilken potential har de? Hur kan vi hitta nya användningsområden med enkla ingrepp? Denna forskning kombinerar hållbarhet och ekonomi och undersöker hur nuvarande trender inom renovering och rivning kan utvecklas.
+Forskning om ombyggnad, 2023-pågående.</t>
   </si>
 </sst>
 </file>
@@ -799,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -817,17 +826,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -835,15 +844,15 @@
     </row>
     <row r="3" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -851,15 +860,15 @@
     </row>
     <row r="4" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3429,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -3449,15 +3458,15 @@
     </row>
     <row r="2" spans="1:8" ht="116" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6047,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -6065,7 +6074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -6076,13 +6085,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2" s="2">
         <v>0.15</v>
@@ -6102,13 +6111,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2">
         <v>0.15</v>
@@ -6119,22 +6128,22 @@
     </row>
     <row r="4" spans="1:8" ht="145" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G4" s="2">
         <v>0.15</v>
@@ -6143,24 +6152,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G5" s="2">
         <v>0.15</v>
@@ -6169,24 +6178,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2">
         <v>0.15</v>
@@ -6195,24 +6204,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="203" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2">
         <v>0.15</v>
@@ -6223,22 +6232,22 @@
     </row>
     <row r="8" spans="1:8" ht="145" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2">
         <v>0.15</v>
@@ -6247,24 +6256,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G9" s="2">
         <v>0.15</v>
@@ -6273,24 +6282,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -8901,7 +8910,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -8916,87 +8925,87 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="232" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="174" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="232" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="261" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -11379,7 +11388,11 @@
   <dimension ref="A1:G268"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="40.6328125" customWidth="1"/>
+    <col min="1" max="1" width="13.6328125" customWidth="1"/>
+    <col min="2" max="3" width="40.6328125" customWidth="1"/>
+    <col min="4" max="4" width="65.90625" customWidth="1"/>
+    <col min="5" max="5" width="68.81640625" customWidth="1"/>
+    <col min="6" max="7" width="40.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -11390,7 +11403,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -11405,53 +11418,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="362.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="319" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="261" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="377" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">
@@ -11460,7 +11473,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93778B2-94A6-4697-9903-ED6869869172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AD40D1-C08A-415B-95AB-B74C8C1DBFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -205,9 +205,6 @@
     <t>**Hur identifierar och utvecklar vi värde?**</t>
   </si>
   <si>
-    <t>Positionerad mellan **praktik, forskning och policy**...</t>
-  </si>
-  <si>
     <t>Intro</t>
   </si>
   <si>
@@ -264,10 +261,6 @@
 More fun</t>
   </si>
   <si>
-    <t>As a society, we are witnessing rapid changes in how we plan, build and live. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources. Unlike generations before us, we are given the chance to pass on an embodied social and cultural heritage.
-We are building for a new future, with the beautiful legacy from before us.</t>
-  </si>
-  <si>
     <t>**Building your legacy**</t>
   </si>
   <si>
@@ -286,31 +279,6 @@
   <si>
     <t>The richness inherited is often irreplaceable. Materials and elaborate craftmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
 **Qualities we so often try to recreate are already present, waiting to be cared for, adapted and brought into new use.**</t>
-  </si>
-  <si>
-    <t>The starting point is observation and evaluation. AAA believes the concrete reality – the materials, structure and layers of use – must be understood to unlock the hidden potential of a building or place.
-* Through **early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
-* This **iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
-* It is **not a phase of design**, but an iterative process of exploring scenarios of the best way forward.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> * AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places. This approach helps property owners and municipalities to understand the existing potential early, before large investments are made or decisions narrow down the possible options.
- * AAA has extensive experience in **leading architecture projects** for a renovation or addition. 
-Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
-  </si>
-  <si>
-    <t>Positioned between **practice, research and policy**...</t>
-  </si>
-  <si>
-    <t>* AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga utvecklingsskeden** för befintliga byggnader och platser. Detta synsätt hjälper fastighetsägare och kommuner att tidigt förstå den befintliga potentialen, innan stora investeringar görs eller beslut begränsar de möjliga alternativen.
-* AAA har lång erfarenhet av **att leda arkitekturprojekt** för renoveringar eller tillägg.
-Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
-  </si>
-  <si>
-    <t>Utgångspunkten är observation och utvärdering. AAA anser att den konkreta verkligheten – materialen, strukturen och användningslagren – måste förstås för att frigöra den dolda potentialen i en byggnad eller plats.
-* Genom **tidig kartläggning** av material, struktur och rumslig logik, utvärderas olika alternativ för återanvändning eller anpassning.
-* Denna **iterativa process** bygger en grund för informerade beslutsfattanden, där miljömässiga, sociala och arkitektoniska kvaliteter integreras från start.
-* Det är **inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
   </si>
   <si>
     <t>**Att utveckla ert arv**</t>
@@ -351,25 +319,7 @@
     <t>Hur kan rum och användning inspireras av de vardagliga miljöerna runt omkring oss? Pågående fotografisk utforskning av atmosfärer och möjligheter i den befintliga miljöer.</t>
   </si>
   <si>
-    <t>... Henrik has been invited to talk or be part of numerous **conferences, discussions and presentations**. Recently at [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/).
-As a specialised practice, AAA often ventures into **collaborations** and has over the years worked with [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). For [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private clients.
-AAA’s work and reflections have been **featured in** [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
-AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB.
-© 2025 Agency for Adaptive Architecture. All rights reserved.</t>
-  </si>
-  <si>
-    <t>... Henrik har blivit inbjuden att tala eller delta i flertalet **konferenser, diskussioner och presentationer**. Nyligen på [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/).
-Som specialiserad praktik ger sig AAA ofta in i **samarbeten** och har genom åren arbetat med [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). För [Riksbyggen](https://www.riksbyggen.se), [Lunds kommun](https://en.lundcity.se/), [Växjö kommun](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privata klienter.
-AAA:s arbete och reflektioner har **uppmärksammats i** [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
-AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB.
-© 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
-  </si>
-  <si>
     <t>In embracing the complexity of an existing building or place – we can do more* – with less**</t>
-  </si>
-  <si>
-    <t>Som samhälle ser vi en snabba förändring i hur vi planerar, bygger och lever. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. Till skillnad från generationer före oss, ges vi chansen att föra vidare ett inbyggt socialt och kulturellt arv.
-Vi bygger för en ny framtid, med det vackra arvet från för.</t>
   </si>
   <si>
     <t>Den rikedom som finns i det vi ärvt är oftast oersättlig. Material och genomarbetat hantverk från tidigare tider, lager av mänsklig prägel och berättelser, en tätt vävd social struktur som skapar mening och tillhörighet, design av bestående kvalitet och karaktär, livfullt mångfacetterade användningsområden och en stark känsla för plats.
@@ -400,6 +350,50 @@
   <si>
     <t>Sättet vi arbetar och lever i staden förändras. Vissa byggnader har svårt att anpassa sig, särskilt kontor från 80-talet. Vilken potential har de? Hur kan vi hitta nya användningsområden med enkla ingrepp? Denna forskning kombinerar hållbarhet och ekonomi och undersöker hur nuvarande trender inom renovering och rivning kan utvecklas.
 Forskning om ombyggnad, 2023-pågående.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places.
+ * AAA has extensive experience in **leading architecture projects** for a renovation or addition. 
+Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
+  </si>
+  <si>
+    <t>* AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga utvecklingsskeden** för befintliga byggnader och platser. 
+* AAA har lång erfarenhet av **att leda arkitekturprojekt** för renoveringar eller tillägg.
+Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
+  </si>
+  <si>
+    <t>As a society, we are witnessing rapid changes in how we plan, build and live. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
+We are building for a new future, with the beautiful legacy from before us.</t>
+  </si>
+  <si>
+    <t>Som samhälle ser vi en snabba förändring i hur vi planerar, bygger och lever. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. 
+Vi bygger för en ny framtid, med det vackra arvet från för.</t>
+  </si>
+  <si>
+    <t>Positioned between **practice, research and policy**</t>
+  </si>
+  <si>
+    <t>Positionerad mellan **praktik, forskning och policy**</t>
+  </si>
+  <si>
+    <t>The starting point is observation and evaluation. AAA believes the concrete reality – the materials, structure and layers of use – must be understood to unlock the potential of a building or place.
+* Through **early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
+* This **iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
+* It is **not a phase of design**, but an iterative process of exploring scenarios of the best way forward.</t>
+  </si>
+  <si>
+    <t>Utgångspunkten är observation och utvärdering. AAA anser att den konkreta verkligheten – materialen, strukturen och användningslagren – måste förstås för att frigöra potentialen i en byggnad eller plats.
+* Genom **tidig kartläggning** av material, struktur och rumslig logik, utvärderas olika alternativ för återanvändning eller anpassning.
+* Denna **iterativa process** bygger en grund för informerade beslutsfattanden, där miljömässiga, sociala och arkitektoniska kvaliteter integreras från start.
+* Det är **inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
+  </si>
+  <si>
+    <t>*Presentationer:* [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). *Samarbeten:* [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). *Kunder:* [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. *Publikationer:* [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
+AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
+  </si>
+  <si>
+    <t>*Presentations*: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). *Collaborations*: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). *Clients*: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. *Publications*: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
+AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
   </si>
 </sst>
 </file>
@@ -828,15 +822,15 @@
     </row>
     <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -844,15 +838,15 @@
     </row>
     <row r="3" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -860,15 +854,15 @@
     </row>
     <row r="4" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3458,15 +3452,15 @@
     </row>
     <row r="2" spans="1:8" ht="116" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6085,10 +6079,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -6140,7 +6134,7 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>31</v>
@@ -6163,10 +6157,10 @@
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>32</v>
@@ -6189,10 +6183,10 @@
         <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>33</v>
@@ -6218,7 +6212,7 @@
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>36</v>
@@ -6241,10 +6235,10 @@
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>40</v>
@@ -6267,10 +6261,10 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>43</v>
@@ -6293,10 +6287,10 @@
         <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>47</v>
@@ -8925,20 +8919,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="174" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="145" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -8953,13 +8947,13 @@
         <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8976,13 +8970,13 @@
         <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -8993,19 +8987,19 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -11425,46 +11419,46 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="319" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="174" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="377" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="261" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AD40D1-C08A-415B-95AB-B74C8C1DBFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB94F09-04F8-4816-858A-72F43014B06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="1" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -211,12 +211,6 @@
     <t>Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning – to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.</t>
   </si>
   <si>
-    <t xml:space="preserve">AAA is an emerging Agency for Adaptive Architecture, working with renovations, additions and strategies for the existing environment. Through the lens of an economic and technical know-how, weaved with ecological and cultural considerations, the present qualities are reinterpreted into a generous and functional space. </t>
-  </si>
-  <si>
-    <t>AAA är en framväxande byrå för anpassningsbar arkitektur som arbetar med renovering, tillägg och strategier för den befintliga miljön. Genom en kombination av ekonomisk och teknisk kunskap, sammanvävd med ekologiska och kulturella hänsyn, omtolkas de befintliga kvaliteterna till generösa och funktionella rum.</t>
-  </si>
-  <si>
     <t>AAA000/AAA02.jpg</t>
   </si>
   <si>
@@ -370,30 +364,36 @@
 Vi bygger för en ny framtid, med det vackra arvet från för.</t>
   </si>
   <si>
-    <t>Positioned between **practice, research and policy**</t>
-  </si>
-  <si>
-    <t>Positionerad mellan **praktik, forskning och policy**</t>
-  </si>
-  <si>
-    <t>The starting point is observation and evaluation. AAA believes the concrete reality – the materials, structure and layers of use – must be understood to unlock the potential of a building or place.
-* Through **early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
-* This **iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
-* It is **not a phase of design**, but an iterative process of exploring scenarios of the best way forward.</t>
-  </si>
-  <si>
-    <t>Utgångspunkten är observation och utvärdering. AAA anser att den konkreta verkligheten – materialen, strukturen och användningslagren – måste förstås för att frigöra potentialen i en byggnad eller plats.
-* Genom **tidig kartläggning** av material, struktur och rumslig logik, utvärderas olika alternativ för återanvändning eller anpassning.
-* Denna **iterativa process** bygger en grund för informerade beslutsfattanden, där miljömässiga, sociala och arkitektoniska kvaliteter integreras från start.
-* Det är **inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
-  </si>
-  <si>
     <t>*Presentationer:* [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). *Samarbeten:* [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). *Kunder:* [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. *Publikationer:* [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
 AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
   </si>
   <si>
     <t>*Presentations*: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). *Collaborations*: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). *Clients*: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. *Publications*: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
 AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
+  </si>
+  <si>
+    <t>The starting point is observation and evaluation. AAA believes the concrete reality, the materials, structure and layers of use, must be understood to unlock the potential of a building or place.
+* Through **early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
+* This **iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
+* It is **not a phase of design**, but an iterative process of exploring scenarios of the best way forward.</t>
+  </si>
+  <si>
+    <t>Utgångspunkten är observation och utvärdering. AAA anser att den konkreta verkligheten, materialen, strukturen och användningslagren, måste förstås för att frigöra potentialen i en byggnad eller plats.
+* Genom **tidig kartläggning** av material, struktur och rumslig logik, utvärderas olika alternativ för återanvändning eller anpassning.
+* Denna **iterativa process** bygger en grund för informerade beslutsfattanden, där miljömässiga, sociala och arkitektoniska kvaliteter integreras från start.
+* Det är **inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
+  </si>
+  <si>
+    <t>**Praktik, forskning och policy**</t>
+  </si>
+  <si>
+    <t>**Practice, research and policy**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAA works with renovations, additions and strategies for the existing environment. Through the lens of an economic and technical know-how, weaved with ecological and cultural considerations, the present qualities are reinterpreted into a generous and functional space. </t>
+  </si>
+  <si>
+    <t>AAA arbetar med renovering, tillägg och strategier för den befintliga miljön. Genom en kombination av ekonomisk och teknisk kunskap, sammanvävd med ekologiska och kulturella hänsyn, omtolkas de befintliga kvaliteterna till generösa och funktionella rum.</t>
   </si>
 </sst>
 </file>
@@ -827,10 +827,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -838,15 +838,15 @@
     </row>
     <row r="3" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -854,15 +854,15 @@
     </row>
     <row r="4" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3450,17 +3450,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6079,10 +6079,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -6134,7 +6134,7 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>31</v>
@@ -6157,10 +6157,10 @@
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>32</v>
@@ -6183,10 +6183,10 @@
         <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>33</v>
@@ -6212,7 +6212,7 @@
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>36</v>
@@ -6235,10 +6235,10 @@
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>40</v>
@@ -6261,10 +6261,10 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>43</v>
@@ -6287,10 +6287,10 @@
         <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>47</v>
@@ -8926,13 +8926,13 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -8947,13 +8947,13 @@
         <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8970,13 +8970,13 @@
         <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -8987,19 +8987,19 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -11422,7 +11422,7 @@
         <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -11436,10 +11436,10 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -11449,16 +11449,16 @@
         <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB94F09-04F8-4816-858A-72F43014B06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3559C7C-754A-4A1B-9DB0-2FA91EC4936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="1" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -229,32 +229,6 @@
     <t>svsv</t>
   </si>
   <si>
-    <t>&amp;ast;&amp;ast;   
-Less costs  
-Less co₂  
-Less disturbance  
-Less resources  
-Less pollution  
-Less monotony  
-Less material   
-Less heavy investment   
-...  
-Less destruction</t>
-  </si>
-  <si>
-    <t>&amp;ast;   
-More culture  
-More patina  
-More diversity  
-More value  
-More memories  
-More attachment  
-More craftmanship  
-More beauty   
-...  
-More fun</t>
-  </si>
-  <si>
     <t>**Building your legacy**</t>
   </si>
   <si>
@@ -394,6 +368,28 @@
   </si>
   <si>
     <t>AAA arbetar med renovering, tillägg och strategier för den befintliga miljön. Genom en kombination av ekonomisk och teknisk kunskap, sammanvävd med ekologiska och kulturella hänsyn, omtolkas de befintliga kvaliteterna till generösa och funktionella rum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;ast;   
+More culture  
+More patina  
+More diversity  
+More value  
+More memories  
+More attachment  
+More craftmanship  
+More beauty   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;ast;&amp;ast;   
+Less costs  
+Less co₂  
+Less disturbance  
+Less resources  
+Less pollution  
+Less monotony  
+Less material   
+Less heavy investment   </t>
   </si>
 </sst>
 </file>
@@ -827,7 +823,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>60</v>
@@ -836,14 +832,14 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>60</v>
@@ -852,14 +848,14 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>60</v>
@@ -3457,10 +3453,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6079,10 +6075,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -6134,7 +6130,7 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>31</v>
@@ -6157,10 +6153,10 @@
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>32</v>
@@ -6183,10 +6179,10 @@
         <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>33</v>
@@ -6212,7 +6208,7 @@
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>36</v>
@@ -6235,10 +6231,10 @@
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>40</v>
@@ -6261,10 +6257,10 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>43</v>
@@ -6287,10 +6283,10 @@
         <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>47</v>
@@ -8926,10 +8922,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>57</v>
@@ -8947,13 +8943,13 @@
         <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8970,10 +8966,10 @@
         <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>55</v>
@@ -8987,16 +8983,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>56</v>
@@ -11422,7 +11418,7 @@
         <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -11436,10 +11432,10 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -11449,16 +11445,16 @@
         <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3559C7C-754A-4A1B-9DB0-2FA91EC4936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADE8762-61CB-4923-A511-E305153FB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -208,9 +208,6 @@
     <t>Intro</t>
   </si>
   <si>
-    <t>Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning – to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.</t>
-  </si>
-  <si>
     <t>AAA000/AAA02.jpg</t>
   </si>
   <si>
@@ -301,9 +298,6 @@
 Varje byggnad och plats presenterar sitt unika fall; metoder måste skräddarsys efter dess specifika behov och potential. **Att navigera i denna skärningspunkt mellan ekonomi och ekologi, kultur och teknik, är AAA:s expertis.**</t>
   </si>
   <si>
-    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära – för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.</t>
-  </si>
-  <si>
     <t xml:space="preserve">The kiosk reacts differently to all of its sides, activating the public space by opening the shutters. I.e., offering a pause for the passer-by, protection for a short standing coffee, calmness for a seated meal or a quick take-a-away. The simple and economical wooden structure is built off site and lifted in place. The versatile design allows the building to adapted to many different uses, prolonging its longevity. 
 Public kiosk 18 sqm, Gothenburg, competition 2022 with Markus Gustafsson, architect engineer, Morgane Martin-Alonzo, architect urbanist. </t>
   </si>
@@ -390,6 +384,12 @@
 Less monotony  
 Less material   
 Less heavy investment   </t>
+  </si>
+  <si>
+    <t>Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.</t>
+  </si>
+  <si>
+    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.</t>
   </si>
 </sst>
 </file>
@@ -823,10 +823,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -834,15 +834,15 @@
     </row>
     <row r="3" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -850,15 +850,15 @@
     </row>
     <row r="4" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3453,10 +3453,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6075,10 +6075,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -6130,7 +6130,7 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>31</v>
@@ -6153,10 +6153,10 @@
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>32</v>
@@ -6179,10 +6179,10 @@
         <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>33</v>
@@ -6208,7 +6208,7 @@
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>36</v>
@@ -6231,10 +6231,10 @@
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>40</v>
@@ -6257,10 +6257,10 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>43</v>
@@ -6283,10 +6283,10 @@
         <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>47</v>
@@ -8922,13 +8922,13 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -8943,13 +8943,13 @@
         <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8966,13 +8966,13 @@
         <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -8983,19 +8983,19 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -11415,10 +11415,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -11432,10 +11432,10 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -11445,16 +11445,16 @@
         <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADE8762-61CB-4923-A511-E305153FB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915939A5-6625-42FE-A579-DCE312E7C0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>AAA024/AAA024_Extending_into_the_Sun_05w.jpg, AAA024/AAA024_Extending_into_the_Sun_02w.jpg, AAA024/AAA024_Extending_into_the_Sun_01w.jpg, AAA024/AAA024_Extending_into_the_Sun_03w.jpg, AAA024/AAA024_Extending_into_the_Sun_04w.jpg, AAA024/AAA024_Extending_into_the_Sun_06w.jpg, AAA024/AAA024_Extending_into_the_Sun_07w.jpg</t>
-  </si>
-  <si>
-    <t>AAA019/AAA019_Generative_Care_06.gif</t>
   </si>
   <si>
     <t>Part three</t>
@@ -314,30 +311,12 @@
 Forskning om ombyggnad, 2023-pågående.</t>
   </si>
   <si>
-    <t xml:space="preserve"> * AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places.
- * AAA has extensive experience in **leading architecture projects** for a renovation or addition. 
-Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
-  </si>
-  <si>
-    <t>* AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga utvecklingsskeden** för befintliga byggnader och platser. 
-* AAA har lång erfarenhet av **att leda arkitekturprojekt** för renoveringar eller tillägg.
-Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
-  </si>
-  <si>
     <t>As a society, we are witnessing rapid changes in how we plan, build and live. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
 We are building for a new future, with the beautiful legacy from before us.</t>
   </si>
   <si>
     <t>Som samhälle ser vi en snabba förändring i hur vi planerar, bygger och lever. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. 
 Vi bygger för en ny framtid, med det vackra arvet från för.</t>
-  </si>
-  <si>
-    <t>*Presentationer:* [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). *Samarbeten:* [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). *Kunder:* [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. *Publikationer:* [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
-AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
-  </si>
-  <si>
-    <t>*Presentations*: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). *Collaborations*: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). *Clients*: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. *Publications*: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
-AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
   </si>
   <si>
     <t>The starting point is observation and evaluation. AAA believes the concrete reality, the materials, structure and layers of use, must be understood to unlock the potential of a building or place.
@@ -386,10 +365,39 @@
 Less heavy investment   </t>
   </si>
   <si>
-    <t>Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.</t>
+    <t xml:space="preserve">Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
+ 1. AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places.
+ 2. AAA has extensive experience in **leading architecture projects** for a renovation or addition. </t>
   </si>
   <si>
-    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.</t>
+    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
+1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga utvecklingsskeden** för befintliga byggnader och platser. 
+2. AAA har lång erfarenhet av **att leda arkitekturprojekt** för renoveringar eller tillägg.</t>
+  </si>
+  <si>
+    <t>AAA019/AAA019_Generative_Care_06.gif, AAA000/Almquist-Henrik-02-lq.jpg</t>
+  </si>
+  <si>
+    <t>*Presentations*: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+*Collaborations*: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
+*Clients*: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
+*Publications*: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
+AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
+  </si>
+  <si>
+    <t>*Presentationer:* [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+*Samarbeten:* [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
+*Kunder:* [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
+*Publikationer:* [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
+AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
+  </si>
+  <si>
+    <t>Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.
+För frågor eller för att diskutera ett projekt är du välkommen att höra av dig på [+46 (0)79 351 34 61](tel:+46793513461) eller [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
+  </si>
+  <si>
+    <t>Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.
+For any inquiries or to discuss a project, you are welcome to get in touch at [+46 (0)79 351 34 61](tel:+46793513461) or [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
   </si>
 </sst>
 </file>
@@ -798,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -818,15 +826,15 @@
     </row>
     <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -834,15 +842,15 @@
     </row>
     <row r="3" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -850,15 +858,15 @@
     </row>
     <row r="4" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3428,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -3448,15 +3456,15 @@
     </row>
     <row r="2" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6046,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -6075,10 +6083,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -6101,10 +6109,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>18</v>
@@ -6118,22 +6126,22 @@
     </row>
     <row r="4" spans="1:8" ht="145" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" s="2">
         <v>0.15</v>
@@ -6144,22 +6152,22 @@
     </row>
     <row r="5" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="2">
         <v>0.15</v>
@@ -6170,22 +6178,22 @@
     </row>
     <row r="6" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2">
         <v>0.15</v>
@@ -6196,22 +6204,22 @@
     </row>
     <row r="7" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2">
         <v>0.15</v>
@@ -6222,22 +6230,22 @@
     </row>
     <row r="8" spans="1:8" ht="145" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2">
         <v>0.15</v>
@@ -6248,22 +6256,22 @@
     </row>
     <row r="9" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2">
         <v>0.15</v>
@@ -6274,22 +6282,22 @@
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -8900,7 +8908,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -8922,13 +8930,13 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -8937,19 +8945,19 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8960,19 +8968,19 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -8983,19 +8991,19 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -11393,7 +11401,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -11408,53 +11416,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="174" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="145" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="261" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">
@@ -11463,7 +11471,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915939A5-6625-42FE-A579-DCE312E7C0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C470C7F-2A29-4B80-8F6D-10E570EB9966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="4010" yWindow="2020" windowWidth="21600" windowHeight="13210" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -311,14 +311,6 @@
 Forskning om ombyggnad, 2023-pågående.</t>
   </si>
   <si>
-    <t>As a society, we are witnessing rapid changes in how we plan, build and live. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
-We are building for a new future, with the beautiful legacy from before us.</t>
-  </si>
-  <si>
-    <t>Som samhälle ser vi en snabba förändring i hur vi planerar, bygger och lever. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. 
-Vi bygger för en ny framtid, med det vackra arvet från för.</t>
-  </si>
-  <si>
     <t>The starting point is observation and evaluation. AAA believes the concrete reality, the materials, structure and layers of use, must be understood to unlock the potential of a building or place.
 * Through **early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
 * This **iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
@@ -365,24 +357,7 @@
 Less heavy investment   </t>
   </si>
   <si>
-    <t xml:space="preserve">Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
- 1. AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places.
- 2. AAA has extensive experience in **leading architecture projects** for a renovation or addition. </t>
-  </si>
-  <si>
-    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
-1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga utvecklingsskeden** för befintliga byggnader och platser. 
-2. AAA har lång erfarenhet av **att leda arkitekturprojekt** för renoveringar eller tillägg.</t>
-  </si>
-  <si>
     <t>AAA019/AAA019_Generative_Care_06.gif, AAA000/Almquist-Henrik-02-lq.jpg</t>
-  </si>
-  <si>
-    <t>*Presentations*: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-*Collaborations*: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
-*Clients*: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
-*Publications*: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
-AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
   </si>
   <si>
     <t>*Presentationer:* [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
@@ -398,6 +373,31 @@
   <si>
     <t>Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.
 For any inquiries or to discuss a project, you are welcome to get in touch at [+46 (0)79 351 34 61](tel:+46793513461) or [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  * *Presentations*: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+*Collaborations*: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
+*Clients*: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
+*Publications*: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
+AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
+  </si>
+  <si>
+    <t>**Through an adaptive approach** we make the most of the rapid change we see of how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
+We are building for a new future, with the beautiful legacy from before us.</t>
+  </si>
+  <si>
+    <t>**Genom ett adaptivt förhållningssätt** tar vi vara på den snabba förändring vi ser i hur vi planerar, bygger och lever som samhälle. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. 
+Vi bygger för en ny framtid, med det vackra arvet från för.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
+ 1. AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places. See what we mean by an [adaptive](#/adaptive) approach.
+ 2. AAA has extensive experience in **leading [architecture](#/architecture) projects** for a renovation or an addition. </t>
+  </si>
+  <si>
+    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
+1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga utvecklingsskeden** för befintliga byggnader och platser. Se vad vi menar med en  [adaptivt](#/adaptive) förhållningssätt. 
+2. AAA har lång erfarenhet av **att leda [arkitekturprojekt](#/architecture)** för renoveringar eller tillägg.</t>
   </si>
 </sst>
 </file>
@@ -847,7 +847,7 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>58</v>
@@ -863,7 +863,7 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>58</v>
@@ -3461,10 +3461,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -8923,17 +8923,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>55</v>
@@ -8974,10 +8974,10 @@
         <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>53</v>
@@ -11416,20 +11416,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="174" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -11440,29 +11440,29 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="348" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C470C7F-2A29-4B80-8F6D-10E570EB9966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABF4B26-34D1-4871-825D-921C38D4A545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4010" yWindow="2020" windowWidth="21600" windowHeight="13210" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
   <si>
     <t>Index</t>
   </si>
@@ -360,44 +360,63 @@
     <t>AAA019/AAA019_Generative_Care_06.gif, AAA000/Almquist-Henrik-02-lq.jpg</t>
   </si>
   <si>
-    <t>*Presentationer:* [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-*Samarbeten:* [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
-*Kunder:* [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
-*Publikationer:* [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
-AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
-  </si>
-  <si>
-    <t>Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.
-För frågor eller för att diskutera ett projekt är du välkommen att höra av dig på [+46 (0)79 351 34 61](tel:+46793513461) eller [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
-  </si>
-  <si>
-    <t>Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.
-For any inquiries or to discuss a project, you are welcome to get in touch at [+46 (0)79 351 34 61](tel:+46793513461) or [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  * *Presentations*: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-*Collaborations*: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
-*Clients*: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
-*Publications*: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
-AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
-  </si>
-  <si>
-    <t>**Through an adaptive approach** we make the most of the rapid change we see of how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
+    <t>**Through an adaptive approach** we respond to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
 We are building for a new future, with the beautiful legacy from before us.</t>
   </si>
   <si>
-    <t>**Genom ett adaptivt förhållningssätt** tar vi vara på den snabba förändring vi ser i hur vi planerar, bygger och lever som samhälle. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. 
+    <t>**Genom ett adaptivt förhållningssätt** svarar vi på de snabba förändringar som präglar hur vi planerar, bygger och lever som samhälle. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. 
 Vi bygger för en ny framtid, med det vackra arvet från för.</t>
   </si>
   <si>
     <t xml:space="preserve">Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
- 1. AAA offers support in navigating, identifying values and finding ways forward in **early-stage developments** for existing buildings and places. See what we mean by an [adaptive](#/adaptive) approach.
+ 1. AAA offers support in navigating, identifying values and finding ways forward through an **[adaptive](#/adaptive) approach in early-stage developments** for existing buildings and places.
  2. AAA has extensive experience in **leading [architecture](#/architecture) projects** for a renovation or an addition. </t>
   </si>
   <si>
+    <t>Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
+Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
+Publications: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
+AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
+  </si>
+  <si>
+    <t>profile</t>
+  </si>
+  <si>
+    <t>For any inquiries or to discuss a project, you are welcome to get in touch at [+46 (0)79 351 34 61](tel:+46793513461) or [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
+  </si>
+  <si>
+    <t>För frågor eller för att diskutera ett projekt är du välkommen att höra av dig på [+46 (0)79 351 34 61](tel:+46793513461) eller [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
+  </si>
+  <si>
+    <t>**Henrik Almquist** tar med sig erfarenhet från..</t>
+  </si>
+  <si>
+    <t>(Grundare, MArch dip. D’État Francaise, Arkitekt SAR/MSA).. Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
+  </si>
+  <si>
     <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
-1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt i **tidiga utvecklingsskeden** för befintliga byggnader och platser. Se vad vi menar med en  [adaptivt](#/adaptive) förhållningssätt. 
+1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en **[adaptivt](#/adaptive) metod i tidiga utvecklingsskeden** för befintliga byggnader och platser. 
 2. AAA har lång erfarenhet av **att leda [arkitekturprojekt](#/architecture)** för renoveringar eller tillägg.</t>
+  </si>
+  <si>
+    <t>Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
+Kunder: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
+Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
+AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
+  </si>
+  <si>
+    <t>Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
+  </si>
+  <si>
+    <t>Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
+  </si>
+  <si>
+    <t>Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
+  </si>
+  <si>
+    <t>AAA000/Almquist_Form-Design-Center-Malmo_w.jpg</t>
   </si>
 </sst>
 </file>
@@ -8930,10 +8949,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>55</v>
@@ -11383,7 +11402,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04093925-E5E8-4C20-AF94-7ABD304FA7F3}">
-  <dimension ref="A1:G268"/>
+  <dimension ref="A1:G269"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="1"/>
@@ -11423,65 +11442,77 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="348" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="333.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2">
+      <c r="E5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -11498,12 +11529,16 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
@@ -13847,6 +13882,15 @@
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
     </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" s="2"/>
+      <c r="B269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+      <c r="E269" s="2"/>
+      <c r="F269" s="2"/>
+      <c r="G269" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABF4B26-34D1-4871-825D-921C38D4A545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F237666-6DC2-4516-BDC7-19AD75782A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="106">
   <si>
     <t>Index</t>
   </si>
@@ -368,11 +368,6 @@
 Vi bygger för en ny framtid, med det vackra arvet från för.</t>
   </si>
   <si>
-    <t xml:space="preserve">Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
- 1. AAA offers support in navigating, identifying values and finding ways forward through an **[adaptive](#/adaptive) approach in early-stage developments** for existing buildings and places.
- 2. AAA has extensive experience in **leading [architecture](#/architecture) projects** for a renovation or an addition. </t>
-  </si>
-  <si>
     <t>Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
 Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
 Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
@@ -389,17 +384,6 @@
     <t>För frågor eller för att diskutera ett projekt är du välkommen att höra av dig på [+46 (0)79 351 34 61](tel:+46793513461) eller [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
   </si>
   <si>
-    <t>**Henrik Almquist** tar med sig erfarenhet från..</t>
-  </si>
-  <si>
-    <t>(Grundare, MArch dip. D’État Francaise, Arkitekt SAR/MSA).. Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
-  </si>
-  <si>
-    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
-1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en **[adaptivt](#/adaptive) metod i tidiga utvecklingsskeden** för befintliga byggnader och platser. 
-2. AAA har lång erfarenhet av **att leda [arkitekturprojekt](#/architecture)** för renoveringar eller tillägg.</t>
-  </si>
-  <si>
     <t>Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
 Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
 Kunder: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
@@ -413,10 +397,29 @@
     <t>Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
   </si>
   <si>
-    <t>Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
+    <t>AAA000/Almquist_Form-Design-Center-Malmo_w.jpg</t>
   </si>
   <si>
-    <t>AAA000/Almquist_Form-Design-Center-Malmo_w.jpg</t>
+    <t>Founded by **Henrik Almquist**, Arkitekt SAR/MSA, Dip. d’État (France)</t>
+  </si>
+  <si>
+    <t>Brings experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
+  </si>
+  <si>
+    <t>Grundat av **Henrik Almquist**, Arkitekt SAR/MSA, Dip. d’État (France)</t>
+  </si>
+  <si>
+    <t>Tar med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
+  </si>
+  <si>
+    <t>Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
+ 1. AAA offers support in navigating, identifying values and finding ways forward through an **[adaptive](#/adaptive) approach in early-stage developments** for existing buildings and places.
+ 2. AAA has extensive experience in **leading [architecture](#/architecture) projects** for renovations or additions, aiming to achieve the greatest effect with the means available.</t>
+  </si>
+  <si>
+    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
+1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en **[adaptivt](#/adaptive) metod i tidiga utvecklingsskeden** för befintliga byggnader och platser. 
+2. AAA har omfattande erfarenhet av  att **leda [arkitekturprojekt](#/architecture)** för renoveringar eller tillägg, med målet att skapa största möjliga värde med de medel som finns tillgängliga.</t>
   </si>
 </sst>
 </file>
@@ -11435,39 +11438,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="203" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -11480,10 +11485,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11499,10 +11504,10 @@
         <v>83</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">
@@ -11534,10 +11539,10 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F237666-6DC2-4516-BDC7-19AD75782A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE08BAC-C13C-4077-8E4A-54A3DD8A8514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
   <si>
     <t>Index</t>
   </si>
@@ -205,13 +205,7 @@
     <t>Intro</t>
   </si>
   <si>
-    <t>AAA000/AAA02.jpg</t>
-  </si>
-  <si>
     <t>AAA000/AAA03.png</t>
-  </si>
-  <si>
-    <t>AAA000/AAA00.jpg</t>
   </si>
   <si>
     <t>More</t>
@@ -237,10 +231,6 @@
   </si>
   <si>
     <t xml:space="preserve">How can space and use be inspired by the everyday environments surrounding us? Ongoing photographic exploration of atmospheres and possibilities in existing settings. </t>
-  </si>
-  <si>
-    <t>The richness inherited is often irreplaceable. Materials and elaborate craftmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
-**Qualities we so often try to recreate are already present, waiting to be cared for, adapted and brought into new use.**</t>
   </si>
   <si>
     <t>**Att utveckla ert arv**</t>
@@ -282,10 +272,6 @@
   </si>
   <si>
     <t>In embracing the complexity of an existing building or place – we can do more* – with less**</t>
-  </si>
-  <si>
-    <t>Den rikedom som finns i det vi ärvt är oftast oersättlig. Material och genomarbetat hantverk från tidigare tider, lager av mänsklig prägel och berättelser, en tätt vävd social struktur som skapar mening och tillhörighet, design av bestående kvalitet och karaktär, livfullt mångfacetterade användningsområden och en stark känsla för plats.
-**Kvaliteter vi så ofta försöker återskapa är redan närvarande, i väntan på att tas om hand, anpassas och ges en ny användning.**</t>
   </si>
   <si>
     <t>AAA har länge arbetat med dessa utmaningar och utvecklat metoder som kombinerar designintelligens, strategiskt beslutsfattande och arkitektonisk erfarenhet.
@@ -368,13 +354,6 @@
 Vi bygger för en ny framtid, med det vackra arvet från för.</t>
   </si>
   <si>
-    <t>Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
-Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
-Publications: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
-AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
-  </si>
-  <si>
     <t>profile</t>
   </si>
   <si>
@@ -382,13 +361,6 @@
   </si>
   <si>
     <t>För frågor eller för att diskutera ett projekt är du välkommen att höra av dig på [+46 (0)79 351 34 61](tel:+46793513461) eller [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
-  </si>
-  <si>
-    <t>Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/). 
-Kunder: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
-Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
-AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
   </si>
   <si>
     <t>Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
@@ -420,6 +392,31 @@
     <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
 1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en **[adaptivt](#/adaptive) metod i tidiga utvecklingsskeden** för befintliga byggnader och platser. 
 2. AAA har omfattande erfarenhet av  att **leda [arkitekturprojekt](#/architecture)** för renoveringar eller tillägg, med målet att skapa största möjliga värde med de medel som finns tillgängliga.</t>
+  </si>
+  <si>
+    <t>The richness inherited is often irreplaceable. Materials and elaborate craftmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
+Qualities we so often try to recreate are already present, waiting to be cared for, adapted and brought into new use.</t>
+  </si>
+  <si>
+    <t>Den rikedom som finns i det vi ärvt är oftast oersättlig. Material och genomarbetat hantverk från tidigare tider, lager av mänsklig prägel och berättelser, en tätt vävd social struktur som skapar mening och tillhörighet, design av bestående kvalitet och karaktär, livfullt mångfacetterade användningsområden och en stark känsla för plats.
+Kvaliteter vi så ofta försöker återskapa är redan närvarande, i väntan på att tas om hand, anpassas och ges en ny användning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
+Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/).
+Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+Publications: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
+AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
+  </si>
+  <si>
+    <t>Kunder: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
+Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/).
+Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
+AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
   </si>
 </sst>
 </file>
@@ -853,10 +850,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -864,15 +861,15 @@
     </row>
     <row r="3" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -880,15 +877,15 @@
     </row>
     <row r="4" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3483,10 +3480,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6105,10 +6102,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -6160,7 +6157,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>30</v>
@@ -6183,10 +6180,10 @@
         <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>31</v>
@@ -6209,10 +6206,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>32</v>
@@ -6238,7 +6235,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>35</v>
@@ -6261,10 +6258,10 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>39</v>
@@ -6287,10 +6284,10 @@
         <v>45</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>42</v>
@@ -6313,10 +6310,10 @@
         <v>48</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>46</v>
@@ -8952,13 +8949,13 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -8973,16 +8970,14 @@
         <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="232" x14ac:dyDescent="0.35">
@@ -8996,13 +8991,13 @@
         <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -9013,19 +9008,19 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -11445,34 +11440,34 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -11485,29 +11480,29 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">
@@ -11539,10 +11534,10 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE08BAC-C13C-4077-8E4A-54A3DD8A8514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C278B7-1BFF-4DB6-8DE2-97EAAE05EE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="3" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="106">
   <si>
     <t>Index</t>
   </si>
@@ -402,9 +402,6 @@
 Kvaliteter vi så ofta försöker återskapa är redan närvarande, i väntan på att tas om hand, anpassas och ges en ny användning.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
 Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/).
 Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
@@ -417,6 +414,12 @@
 Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
 Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
 AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
+  </si>
+  <si>
+    <t>AAA000/AAA02.jpg</t>
+  </si>
+  <si>
+    <t>AAA000/AAA00.jpg</t>
   </si>
 </sst>
 </file>
@@ -8975,9 +8978,11 @@
       <c r="E3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="G3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="232" x14ac:dyDescent="0.35">
@@ -8997,7 +9002,7 @@
         <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -11499,10 +11504,10 @@
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C278B7-1BFF-4DB6-8DE2-97EAAE05EE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00587D6F-C4A6-47BF-AFB8-CA9663F3BAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="3" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="108">
   <si>
     <t>Index</t>
   </si>
@@ -402,24 +402,30 @@
 Kvaliteter vi så ofta försöker återskapa är redan närvarande, i väntan på att tas om hand, anpassas och ges en ny användning.</t>
   </si>
   <si>
+    <t>AAA000/AAA02.jpg</t>
+  </si>
+  <si>
+    <t>AAA000/AAA00.jpg</t>
+  </si>
+  <si>
     <t>Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
-Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/).
+Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
 Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
 Publications: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
 AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
   </si>
   <si>
     <t>Kunder: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
-Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/).
+Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
 Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
 Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
 AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
   </si>
   <si>
-    <t>AAA000/AAA02.jpg</t>
+    <t>For any inquiries or to discuss a project, welcome to [call](tel:+46793513461) / [mail](mailto:contact@a-a-a.se)</t>
   </si>
   <si>
-    <t>AAA000/AAA00.jpg</t>
+    <t>För frågor eller för att diskutera ett projekt, välkommen att [ringa](tel:+46793513461) / [maila](mailto:contact@a-a-a.se)</t>
   </si>
 </sst>
 </file>
@@ -8979,7 +8985,7 @@
         <v>101</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -9002,7 +9008,7 @@
         <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -11478,17 +11484,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11504,10 +11510,10 @@
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">
@@ -11565,12 +11571,16 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00587D6F-C4A6-47BF-AFB8-CA9663F3BAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE125F69-8D03-4729-8165-024776F24795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
   <si>
     <t>Index</t>
   </si>
@@ -355,18 +355,6 @@
   </si>
   <si>
     <t>profile</t>
-  </si>
-  <si>
-    <t>For any inquiries or to discuss a project, you are welcome to get in touch at [+46 (0)79 351 34 61](tel:+46793513461) or [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
-  </si>
-  <si>
-    <t>För frågor eller för att diskutera ett projekt är du välkommen att höra av dig på [+46 (0)79 351 34 61](tel:+46793513461) eller [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
-  </si>
-  <si>
-    <t>Founded by **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) who brings experience from Stockholm, Paris and Tokyo. He has carried out projects from in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
-  </si>
-  <si>
-    <t>Grundat av **Henrik Almquist** (MArch dip. D’État Francaise, Arkitekt SAR/MSA) som har med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
   </si>
   <si>
     <t>AAA000/Almquist_Form-Design-Center-Malmo_w.jpg</t>
@@ -8979,13 +8967,13 @@
         <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -9008,7 +8996,7 @@
         <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -11451,10 +11439,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>85</v>
@@ -11466,19 +11454,19 @@
         <v>88</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -11491,10 +11479,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11510,10 +11498,10 @@
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">
@@ -11540,16 +11528,12 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
@@ -11571,16 +11555,12 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE125F69-8D03-4729-8165-024776F24795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB431B5D-4310-4861-BE2E-37105ABACDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -410,10 +410,10 @@
 AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
   </si>
   <si>
-    <t>For any inquiries or to discuss a project, welcome to [call](tel:+46793513461) / [mail](mailto:contact@a-a-a.se)</t>
+    <t>For any inquiries or to discuss a project, you are welcome to get in touch at [+46 (0)79 351 34 61](tel:+46793513461) or [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
   </si>
   <si>
-    <t>För frågor eller för att diskutera ett projekt, välkommen att [ringa](tel:+46793513461) / [maila](mailto:contact@a-a-a.se)</t>
+    <t>För frågor eller för att diskutera ett projekt är du välkommen att höra av dig på [+46 (0)79 351 34 61](tel:+46793513461) eller [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
   </si>
 </sst>
 </file>
@@ -11472,7 +11472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB431B5D-4310-4861-BE2E-37105ABACDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785A8691-65F0-4BA3-8D81-FA48FB6A22FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -312,9 +312,6 @@
     <t>**Praktik, forskning och policy**</t>
   </si>
   <si>
-    <t>**Practice, research and policy**</t>
-  </si>
-  <si>
     <t xml:space="preserve">AAA works with renovations, additions and strategies for the existing environment. Through the lens of an economic and technical know-how, weaved with ecological and cultural considerations, the present qualities are reinterpreted into a generous and functional space. </t>
   </si>
   <si>
@@ -360,9 +357,6 @@
     <t>AAA000/Almquist_Form-Design-Center-Malmo_w.jpg</t>
   </si>
   <si>
-    <t>Founded by **Henrik Almquist**, Arkitekt SAR/MSA, Dip. d’État (France)</t>
-  </si>
-  <si>
     <t>Brings experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
   </si>
   <si>
@@ -370,11 +364,6 @@
   </si>
   <si>
     <t>Tar med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
-  </si>
-  <si>
-    <t>Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
- 1. AAA offers support in navigating, identifying values and finding ways forward through an **[adaptive](#/adaptive) approach in early-stage developments** for existing buildings and places.
- 2. AAA has extensive experience in **leading [architecture](#/architecture) projects** for renovations or additions, aiming to achieve the greatest effect with the means available.</t>
   </si>
   <si>
     <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
@@ -410,10 +399,21 @@
 AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
   </si>
   <si>
-    <t>For any inquiries or to discuss a project, you are welcome to get in touch at [+46 (0)79 351 34 61](tel:+46793513461) or [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
+    <t>Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
+(I) AAA offers support in navigating, identifying values and finding ways forward through an **[adaptive](#/adaptive) approach in early-stage developments** for existing buildings and places.
+(II) AAA has extensive experience in **leading [architecture](#/architecture) projects** for renovations or additions, aiming to achieve the greatest effect with the means available.</t>
   </si>
   <si>
-    <t>För frågor eller för att diskutera ett projekt är du välkommen att höra av dig på [+46 (0)79 351 34 61](tel:+46793513461) eller [contact@a-a-a.se](mailto:contact@a-a-a.se)</t>
+    <t>Founded by Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État (France)</t>
+  </si>
+  <si>
+    <t>Practice, research and policy</t>
+  </si>
+  <si>
+    <t>Hör gärna av er [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
+  </si>
+  <si>
+    <t>Get in touch [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
   </si>
 </sst>
 </file>
@@ -863,7 +863,7 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>56</v>
@@ -879,7 +879,7 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>56</v>
@@ -3477,10 +3477,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -8946,10 +8946,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>58</v>
@@ -8967,13 +8967,13 @@
         <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8996,7 +8996,7 @@
         <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -11439,50 +11439,50 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11492,16 +11492,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785A8691-65F0-4BA3-8D81-FA48FB6A22FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB09905-BA1E-464A-9FE4-2F60CD5AA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -309,9 +309,6 @@
 * Det är **inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
   </si>
   <si>
-    <t>**Praktik, forskning och policy**</t>
-  </si>
-  <si>
     <t xml:space="preserve">AAA works with renovations, additions and strategies for the existing environment. Through the lens of an economic and technical know-how, weaved with ecological and cultural considerations, the present qualities are reinterpreted into a generous and functional space. </t>
   </si>
   <si>
@@ -358,9 +355,6 @@
   </si>
   <si>
     <t>Brings experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
-  </si>
-  <si>
-    <t>Grundat av **Henrik Almquist**, Arkitekt SAR/MSA, Dip. d’État (France)</t>
   </si>
   <si>
     <t>Tar med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
@@ -414,6 +408,12 @@
   </si>
   <si>
     <t>Get in touch [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
+  </si>
+  <si>
+    <t>Praktik, forskning och policy</t>
+  </si>
+  <si>
+    <t>Grundat av Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État (France)</t>
   </si>
 </sst>
 </file>
@@ -863,7 +863,7 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>56</v>
@@ -879,7 +879,7 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>56</v>
@@ -3477,10 +3477,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -8946,10 +8946,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>58</v>
@@ -8967,13 +8967,13 @@
         <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8996,7 +8996,7 @@
         <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -11439,34 +11439,34 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -11479,10 +11479,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11492,16 +11492,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB09905-BA1E-464A-9FE4-2F60CD5AA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73E8B43-03A8-4C78-A6C3-FBBCDBAFE375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="3" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -360,11 +360,6 @@
     <t>Tar med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
   </si>
   <si>
-    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
-1. AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en **[adaptivt](#/adaptive) metod i tidiga utvecklingsskeden** för befintliga byggnader och platser. 
-2. AAA har omfattande erfarenhet av  att **leda [arkitekturprojekt](#/architecture)** för renoveringar eller tillägg, med målet att skapa största möjliga värde med de medel som finns tillgängliga.</t>
-  </si>
-  <si>
     <t>The richness inherited is often irreplaceable. Materials and elaborate craftmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
 Qualities we so often try to recreate are already present, waiting to be cared for, adapted and brought into new use.</t>
   </si>
@@ -404,9 +399,6 @@
     <t>Practice, research and policy</t>
   </si>
   <si>
-    <t>Hör gärna av er [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
-  </si>
-  <si>
     <t>Get in touch [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
   </si>
   <si>
@@ -414,6 +406,14 @@
   </si>
   <si>
     <t>Grundat av Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État (France)</t>
+  </si>
+  <si>
+    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
+(I) AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en **[adaptivt](#/adaptive) metod i tidiga utvecklingsskeden** för befintliga byggnader och platser. 
+(II) AAA har omfattande erfarenhet av  att **leda [arkitekturprojekt](#/architecture)** för renoveringar eller tillägg, med målet att skapa största möjliga värde med de medel som finns tillgängliga.</t>
+  </si>
+  <si>
+    <t>Hör av er [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
   </si>
 </sst>
 </file>
@@ -8967,13 +8967,13 @@
         <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8996,7 +8996,7 @@
         <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -11439,10 +11439,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>83</v>
@@ -11454,10 +11454,10 @@
         <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>88</v>
@@ -11479,10 +11479,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11492,16 +11492,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73E8B43-03A8-4C78-A6C3-FBBCDBAFE375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B1F4DB-1A9D-4336-AA92-1521FB9E9132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="3" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="103">
   <si>
     <t>Index</t>
   </si>
@@ -223,13 +223,6 @@
     <t>AAA000/Potential.gif</t>
   </si>
   <si>
-    <t>AAA has long worked with these challenges, developing methods that combine design intelligence, strategic decision-making and architectural experience.
-* In Växjö AAA received first prize for a reuse strategy of Växjö hospital. 
-* Together with the property developer Riksbyggen, AAA is currently exploring adaptive reuse alternatives of an office and workshop building in Stockholm working with *generative AI*.
-* Recurrently AAA is invited to speak on the evolving practices and sustainable strategies for urban planning.
-Each building and place presents its own unique case; methods must be tailored to its specific needs and potential. **Navigating this intersection of economy and ecology, culture and technology, is AAA’s expertise.**</t>
-  </si>
-  <si>
     <t xml:space="preserve">How can space and use be inspired by the everyday environments surrounding us? Ongoing photographic exploration of atmospheres and possibilities in existing settings. </t>
   </si>
   <si>
@@ -274,13 +267,6 @@
     <t>In embracing the complexity of an existing building or place – we can do more* – with less**</t>
   </si>
   <si>
-    <t>AAA har länge arbetat med dessa utmaningar och utvecklat metoder som kombinerar designintelligens, strategiskt beslutsfattande och arkitektonisk erfarenhet.
-* I Växjö mottog AAA första pris för en återanvändningsstrategi för Växjö sjukhus.
-* Tillsammans med fastighetsutvecklaren Riksbyggen undersöker AAA för närvarande alternativa anpassningar och återanvändningar av en kontors- och verkstadsbyggnad i Stockholm med hjälp av *generativ AI*.
-* AAA bjuds återkommande in för att tala om utvecklingen av praktiken och hållbara strategier för stadsplanering.
-Varje byggnad och plats presenterar sitt unika fall; metoder måste skräddarsys efter dess specifika behov och potential. **Att navigera i denna skärningspunkt mellan ekonomi och ekologi, kultur och teknik, är AAA:s expertis.**</t>
-  </si>
-  <si>
     <t xml:space="preserve">The kiosk reacts differently to all of its sides, activating the public space by opening the shutters. I.e., offering a pause for the passer-by, protection for a short standing coffee, calmness for a seated meal or a quick take-a-away. The simple and economical wooden structure is built off site and lifted in place. The versatile design allows the building to adapted to many different uses, prolonging its longevity. 
 Public kiosk 18 sqm, Gothenburg, competition 2022 with Markus Gustafsson, architect engineer, Morgane Martin-Alonzo, architect urbanist. </t>
   </si>
@@ -295,18 +281,6 @@
   <si>
     <t>Sättet vi arbetar och lever i staden förändras. Vissa byggnader har svårt att anpassa sig, särskilt kontor från 80-talet. Vilken potential har de? Hur kan vi hitta nya användningsområden med enkla ingrepp? Denna forskning kombinerar hållbarhet och ekonomi och undersöker hur nuvarande trender inom renovering och rivning kan utvecklas.
 Forskning om ombyggnad, 2023-pågående.</t>
-  </si>
-  <si>
-    <t>The starting point is observation and evaluation. AAA believes the concrete reality, the materials, structure and layers of use, must be understood to unlock the potential of a building or place.
-* Through **early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
-* This **iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
-* It is **not a phase of design**, but an iterative process of exploring scenarios of the best way forward.</t>
-  </si>
-  <si>
-    <t>Utgångspunkten är observation och utvärdering. AAA anser att den konkreta verkligheten, materialen, strukturen och användningslagren, måste förstås för att frigöra potentialen i en byggnad eller plats.
-* Genom **tidig kartläggning** av material, struktur och rumslig logik, utvärderas olika alternativ för återanvändning eller anpassning.
-* Denna **iterativa process** bygger en grund för informerade beslutsfattanden, där miljömässiga, sociala och arkitektoniska kvaliteter integreras från start.
-* Det är **inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
   </si>
   <si>
     <t xml:space="preserve">AAA works with renovations, additions and strategies for the existing environment. Through the lens of an economic and technical know-how, weaved with ecological and cultural considerations, the present qualities are reinterpreted into a generous and functional space. </t>
@@ -354,12 +328,6 @@
     <t>AAA000/Almquist_Form-Design-Center-Malmo_w.jpg</t>
   </si>
   <si>
-    <t>Brings experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
-  </si>
-  <si>
-    <t>Tar med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
-  </si>
-  <si>
     <t>The richness inherited is often irreplaceable. Materials and elaborate craftmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
 Qualities we so often try to recreate are already present, waiting to be cared for, adapted and brought into new use.</t>
   </si>
@@ -388,14 +356,6 @@
 AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
   </si>
   <si>
-    <t>Every building, every situation holds a **hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
-(I) AAA offers support in navigating, identifying values and finding ways forward through an **[adaptive](#/adaptive) approach in early-stage developments** for existing buildings and places.
-(II) AAA has extensive experience in **leading [architecture](#/architecture) projects** for renovations or additions, aiming to achieve the greatest effect with the means available.</t>
-  </si>
-  <si>
-    <t>Founded by Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État (France)</t>
-  </si>
-  <si>
     <t>Practice, research and policy</t>
   </si>
   <si>
@@ -405,15 +365,54 @@
     <t>Praktik, forskning och policy</t>
   </si>
   <si>
-    <t>Grundat av Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État (France)</t>
+    <t>Hör av er [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
   </si>
   <si>
-    <t>Varje byggnad, varje situation, rymmer en **dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
-(I) AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en **[adaptivt](#/adaptive) metod i tidiga utvecklingsskeden** för befintliga byggnader och platser. 
-(II) AAA har omfattande erfarenhet av  att **leda [arkitekturprojekt](#/architecture)** för renoveringar eller tillägg, med målet att skapa största möjliga värde med de medel som finns tillgängliga.</t>
+    <t>**Every building, every situation holds a hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
+(I) AAA offers support in navigating, identifying values and finding ways forward through an [adaptive approach in early-stage developments](#/adaptive) for existing buildings and places.
+(II) AAA has extensive experience in [leading architecture projects](#/architecture) for renovations or additions, aiming to achieve the greatest effect with the means available.</t>
   </si>
   <si>
-    <t>Hör av er [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
+    <t>Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État (France)</t>
+  </si>
+  <si>
+    <t>Funded AAA 2024, bringing experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
+  </si>
+  <si>
+    <t>**Varje byggnad, varje situation, rymmer en dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
+(I) AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en [adaptiv metod i tidiga utvecklingsskeden](#/adaptive) för befintliga byggnader och platser. 
+(II) AAA har omfattande erfarenhet av [att leda arkitekturprojekt](#/architecture) för renoveringar eller tillägg, med målet att skapa största möjliga värde med de medel som finns tillgängliga.</t>
+  </si>
+  <si>
+    <t>Grundade AAA 2024, tar med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
+  </si>
+  <si>
+    <t>Utgångspunkten är observation och utvärdering. AAA anser att den konkreta verkligheten, materialen, strukturen och användningslagren, måste förstås för att frigöra potentialen i en byggnad eller plats.
+* **Genom tidig kartläggning** av material, struktur och rumslig logik, utvärderas olika alternativ för återanvändning eller anpassning.
+* **Denna iterativa process** bygger en grund för informerade beslutsfattanden, där miljömässiga, sociala och arkitektoniska kvaliteter integreras från start.
+* **Det är inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
+  </si>
+  <si>
+    <t>The starting point is observation and evaluation. AAA believes the concrete reality, the materials, structure and layers of use, must be understood to unlock the potential of a building or place.
+* **Through early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
+* **This iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
+* **It is not a phase of design**, but an iterative process of exploring scenarios of the best way forward.</t>
+  </si>
+  <si>
+    <t>AAA has long worked with these challenges, developing methods that combine design intelligence, strategic decision-making and architectural experience.
+* In Växjö AAA received first prize for a reuse strategy of Växjö hospital. 
+* Together with the property developer Riksbyggen, AAA is currently exploring adaptive reuse alternatives of an office and workshop building in Stockholm working with *generative AI*.
+* Recurrently AAA is invited to speak on the evolving practices and sustainable strategies for urban planning.
+Each building and place presents its own unique case; methods must be tailored to its specific needs and potential. 
+**Navigating this intersection of economy and ecology, culture and technology, is AAA’s expertise.**</t>
+  </si>
+  <si>
+    <t>AAA har länge arbetat med dessa utmaningar och utvecklat metoder som kombinerar designintelligens, strategiskt beslutsfattande och arkitektonisk erfarenhet.
+* I Växjö mottog AAA första pris för en återanvändningsstrategi för Växjö sjukhus.
+* Tillsammans med fastighetsutvecklaren Riksbyggen undersöker AAA för närvarande alternativa anpassningar och återanvändningar av en kontors- och verkstadsbyggnad i Stockholm med hjälp av *generativ AI*.
+* AAA bjuds återkommande in för att tala om utvecklingen av praktiken och hållbara strategier för stadsplanering.
+Varje byggnad och plats presenterar sitt unika fall; metoder måste skräddarsys efter dess specifika behov och potential.
+**Att navigera i denna skärningspunkt mellan ekonomi och ekologi, kultur och teknik, är AAA:s expertis.**</t>
   </si>
 </sst>
 </file>
@@ -847,7 +846,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>56</v>
@@ -863,7 +862,7 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>56</v>
@@ -879,7 +878,7 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>56</v>
@@ -3477,10 +3476,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6099,10 +6098,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -6154,7 +6153,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>30</v>
@@ -6177,10 +6176,10 @@
         <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>31</v>
@@ -6203,10 +6202,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>32</v>
@@ -6232,7 +6231,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>35</v>
@@ -6255,10 +6254,10 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>39</v>
@@ -6281,10 +6280,10 @@
         <v>45</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>42</v>
@@ -6307,10 +6306,10 @@
         <v>48</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>46</v>
@@ -8946,10 +8945,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>58</v>
@@ -8967,13 +8966,13 @@
         <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8990,19 +8989,19 @@
         <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -9010,13 +9009,13 @@
         <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>53</v>
@@ -11439,34 +11438,34 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -11479,10 +11478,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11492,16 +11491,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B1F4DB-1A9D-4336-AA92-1521FB9E9132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4AE5A1-4BD8-4A84-98F0-975C3BD2AC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
   <si>
     <t>Index</t>
   </si>
@@ -342,20 +342,6 @@
     <t>AAA000/AAA00.jpg</t>
   </si>
   <si>
-    <t>Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
-Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
-Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-Publications: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
-AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
-  </si>
-  <si>
-    <t>Kunder: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
-Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
-Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Plan](https://www.planering.org/om-plan).
-AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
-  </si>
-  <si>
     <t>Practice, research and policy</t>
   </si>
   <si>
@@ -374,9 +360,6 @@
   </si>
   <si>
     <t>Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État (France)</t>
-  </si>
-  <si>
-    <t>Funded AAA 2024, bringing experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
   </si>
   <si>
     <t>**Varje byggnad, varje situation, rymmer en dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
@@ -413,6 +396,29 @@
 * AAA bjuds återkommande in för att tala om utvecklingen av praktiken och hållbara strategier för stadsplanering.
 Varje byggnad och plats presenterar sitt unika fall; metoder måste skräddarsys efter dess specifika behov och potential.
 **Att navigera i denna skärningspunkt mellan ekonomi och ekologi, kultur och teknik, är AAA:s expertis.**</t>
+  </si>
+  <si>
+    <t>Founded AAA 2024, bringing experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
+  </si>
+  <si>
+    <t>Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
+Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
+Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+Publications: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Aftonbladet](https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
+AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
+  </si>
+  <si>
+    <t>Kunder: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
+Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
+Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Aftonbladet](https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
+AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
+  </si>
+  <si>
+    <t>artiklar länkar</t>
+  </si>
+  <si>
+    <t>https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst</t>
   </si>
 </sst>
 </file>
@@ -8989,10 +8995,10 @@
         <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>86</v>
@@ -9012,10 +9018,10 @@
         <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>53</v>
@@ -11438,10 +11444,10 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
@@ -11453,16 +11459,16 @@
         <v>82</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -11478,10 +11484,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -11491,16 +11497,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">
@@ -11564,8 +11570,12 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4AE5A1-4BD8-4A84-98F0-975C3BD2AC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95333698-08D9-441C-9649-CF09E5FBD1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="122">
   <si>
     <t>Index</t>
   </si>
@@ -99,9 +99,6 @@
     <t>AAA024/AAA024_Extending_into_the_Sun_05w.jpg, AAA024/AAA024_Extending_into_the_Sun_02w.jpg, AAA024/AAA024_Extending_into_the_Sun_01w.jpg, AAA024/AAA024_Extending_into_the_Sun_03w.jpg, AAA024/AAA024_Extending_into_the_Sun_04w.jpg, AAA024/AAA024_Extending_into_the_Sun_06w.jpg, AAA024/AAA024_Extending_into_the_Sun_07w.jpg</t>
   </si>
   <si>
-    <t>Part three</t>
-  </si>
-  <si>
     <t>**What can an existing building or place offer?**</t>
   </si>
   <si>
@@ -114,18 +111,10 @@
     <t>TitleSv</t>
   </si>
   <si>
-    <t xml:space="preserve">The renovated façade is animated by its new inhabitants; a rich biodiversity of deep soil, people opening up their apartments outside and natural integration of solar power production. A new language for the city of Barcelona marking an important entrance to the historical city and a park. 
-Façade renovation for the City of Barcelona 1'100 sqm, competition 2024 organised by Fundació Mies Van Der Rohe, UIA, UNESCO. </t>
-  </si>
-  <si>
     <t>Casa Mangabeira</t>
   </si>
   <si>
     <t>AAA012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walls are moved, removed and added, finding new uses and enhancing dormant qualities in the building. The 70s villa is opened up between the internal spaces as well as there are new openings excavated towards the outside. A room for meditation is extended in the back, offering a view of a new garden.
-Renovation private residence 300 sqm, Belo Horizonte Brazil, design proposal 2023. </t>
   </si>
   <si>
     <t>AAA017</t>
@@ -158,10 +147,6 @@
     <t>Sofielund</t>
   </si>
   <si>
-    <t>The task lies in interacting with what already exists and to propose a solution of continuity. Acting on all the scales of the city, this project proposes a design approach of an active form. By defining a protocol, a new balance is expressed between the specificity of the local spaces/practices and the market driven urbanisation, while also giving form to an interstitial space that assures a temporality of use. 
-Development strategy for Sofielund Industrial Area, Malmö Sweden, MArch at ENSA Paris Malaquais 2020.</t>
-  </si>
-  <si>
     <t>AAA020/AAA020_Vacant_Potential_01.jpg, AAA020/AAA020_Vacant_Potential_02.jpg, AAA020/AAA020_Vacant_Potential_03.jpg, AAA020/AAA020_Vacant_Potential_04.jpg</t>
   </si>
   <si>
@@ -184,9 +169,6 @@
   </si>
   <si>
     <t>AAAvisualdiary/AAAvisualdiary000.jpg</t>
-  </si>
-  <si>
-    <t>AAA</t>
   </si>
   <si>
     <t>Visual Diary</t>
@@ -223,26 +205,11 @@
     <t>AAA000/Potential.gif</t>
   </si>
   <si>
-    <t xml:space="preserve">How can space and use be inspired by the everyday environments surrounding us? Ongoing photographic exploration of atmospheres and possibilities in existing settings. </t>
-  </si>
-  <si>
     <t>**Att utveckla ert arv**</t>
   </si>
   <si>
     <t>Centralt i Växjö ställde uppdraget frågan: vad händer om vi börjar i det som redan finns? Inom sjukhusområdet prövas en framtid för vårdens arkitektur där de befintliga byggnaderna återbrukas och byggs på. Förslaget introducerar en ny typologi med delade utrymmen och dagsljus, där sjukhusparken flätas samman med vårdmiljöerna. Arbetet kombinerar strategisk utveckling med konkreta rumsliga grepp för att lära av platsen och låta det ta form.
 Utvecklingsstrategi för Växjö kommun, tävling 2023–pågående med  Morgane Martin-Alonzo, arkitekt stadsplanerare, Oscar Aparicio Chavez, arkitekt, Léa Ganteil, arkitekt återbruk.</t>
-  </si>
-  <si>
-    <t>Centrally located in Växjö, the brief asked, what happens with the whole built environment if the hospital moves? We proposed a first phase with three interventions that helps the city to understand how the existing structures can be reused, at the same time, mediating what citizens are expecting. The second phase is a hypothesis of what could be learnt from the site and how that would take form.
-Development strategy för Växjö municipality, competition 2023–ongoing with Morgane Martin-Alonzo, architect urbanist, Oscar Aparicio Chavez, architect, Léa Ganteil, architect reuse.</t>
-  </si>
-  <si>
-    <t>The new church, surrounded by greenery, is a central part of Trondheim’s east. A large square in front creates space for activities and highlights the building. Its design combines a timeless main space with adaptable rooms. A green landscape wall creates a calm courtyard while reused materials, optimised space and design integrated solar panels ensures the building's longevity.
-Church in Trondheim 1’400 sqm, competition 2023 with Markus Gustafsson, architect engineer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entering the courtyard all visitors are struck by the vivid activity in the space, a constantly changing landscape full of impressions. Built from reusable materials, the structure creates an open framework that gives space to what is already there to grow. The sound from the courtyard is recorded, delayed one day and then replayed in the interior acoustically separated room, offering a sort of collective memory. 
-Meeting pavilion 15 sqm, Art Fair Charlottenborg Copenhagen, competition 2023 with Morgane Martin-Alonzo, architect urbanist. </t>
   </si>
   <si>
     <t>Väggar flyttas, tas bort och läggs till, vilket hittar nya användningsområden och förstärker vilande kvaliteter i byggnaden. Den 70-talsvillan öppnas upp mellan de interna ytorna samtidigt som nya öppningar grävs ut mot utsidan. Ett rum för meditation utökas i bakre delen och erbjuder utsikt över en ny trädgård.
@@ -267,23 +234,12 @@
     <t>In embracing the complexity of an existing building or place – we can do more* – with less**</t>
   </si>
   <si>
-    <t xml:space="preserve">The kiosk reacts differently to all of its sides, activating the public space by opening the shutters. I.e., offering a pause for the passer-by, protection for a short standing coffee, calmness for a seated meal or a quick take-a-away. The simple and economical wooden structure is built off site and lifted in place. The versatile design allows the building to adapted to many different uses, prolonging its longevity. 
-Public kiosk 18 sqm, Gothenburg, competition 2022 with Markus Gustafsson, architect engineer, Morgane Martin-Alonzo, architect urbanist. </t>
-  </si>
-  <si>
     <t>Kiosken reagerar olika på alla sina sidor och aktiverar det offentliga rummet genom att öppna luckorna. Den kan till exempel erbjuda en paus för förbipasserande, skydd för en snabb ståfika, lugn för en sittande måltid eller en snabb take-away. Den enkla och ekonomiska träkonstruktionen byggs på annan plats och lyfts på plats. Den mångsidiga designen gör att byggnaden kan anpassas till många olika användningsområden, vilket förlänger dess livslängd.
 Offentlig kiosk 18 kvm, Göteborg, tävling 2022 med Markus Gustafsson, arkitekt ingenjör, Morgane Martin-Alonzo, arkitekt stadsplanerare.</t>
   </si>
   <si>
-    <t>The way we work and live in the city is changing. Some buildings are having a hard time to adapt, especially offices from the 80s. What are their potential? How can we find new uses with simple interventions? Combining sustainability and economy, this research explores how current trends of renovation and demolition can evolve.
-Research on renovations, 2023-ongoing.</t>
-  </si>
-  <si>
     <t>Sättet vi arbetar och lever i staden förändras. Vissa byggnader har svårt att anpassa sig, särskilt kontor från 80-talet. Vilken potential har de? Hur kan vi hitta nya användningsområden med enkla ingrepp? Denna forskning kombinerar hållbarhet och ekonomi och undersöker hur nuvarande trender inom renovering och rivning kan utvecklas.
 Forskning om ombyggnad, 2023-pågående.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAA works with renovations, additions and strategies for the existing environment. Through the lens of an economic and technical know-how, weaved with ecological and cultural considerations, the present qualities are reinterpreted into a generous and functional space. </t>
   </si>
   <si>
     <t>AAA arbetar med renovering, tillägg och strategier för den befintliga miljön. Genom en kombination av ekonomisk och teknisk kunskap, sammanvävd med ekologiska och kulturella hänsyn, omtolkas de befintliga kvaliteterna till generösa och funktionella rum.</t>
@@ -314,10 +270,6 @@
     <t>AAA019/AAA019_Generative_Care_06.gif, AAA000/Almquist-Henrik-02-lq.jpg</t>
   </si>
   <si>
-    <t>**Through an adaptive approach** we respond to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
-We are building for a new future, with the beautiful legacy from before us.</t>
-  </si>
-  <si>
     <t>**Genom ett adaptivt förhållningssätt** svarar vi på de snabba förändringar som präglar hur vi planerar, bygger och lever som samhälle. En byggnad kan stå i över 100 år, medan ett rum kan byta användningsområde snabbt. Omsorg om miljön och de byggnader vi redan har utmanar oss att vara kreativa och att på bästa sätt nyttja våra ekonomiska och ekologiska resurser. 
 Vi bygger för en ny framtid, med det vackra arvet från för.</t>
   </si>
@@ -342,29 +294,13 @@
     <t>AAA000/AAA00.jpg</t>
   </si>
   <si>
-    <t>Practice, research and policy</t>
-  </si>
-  <si>
-    <t>Get in touch [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
-  </si>
-  <si>
     <t>Praktik, forskning och policy</t>
   </si>
   <si>
     <t>Hör av er [+46793513461](tel:+46793513461) / contact@a-a-a.se</t>
   </si>
   <si>
-    <t>**Every building, every situation holds a hidden potential**. AAA’s role as architects is to recognise and elevate these qualities. Whether it's a single building or a whole urban area, subtle adjustments can create a significant impact, transforming how a space feels and functions. AAA’s approach is rooted in listening and learning, to create strategies and designs that harmonise with the environment and respond to the unique needs of each client.
-(I) AAA offers support in navigating, identifying values and finding ways forward through an [adaptive approach in early-stage developments](#/adaptive) for existing buildings and places.
-(II) AAA has extensive experience in [leading architecture projects](#/architecture) for renovations or additions, aiming to achieve the greatest effect with the means available.</t>
-  </si>
-  <si>
     <t>Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État (France)</t>
-  </si>
-  <si>
-    <t>**Varje byggnad, varje situation, rymmer en dold potential**. AAA:s roll som arkitekter är att identifiera och lyfta fram dessa kvaliteter. Oavsett om det rör sig om en enskild byggnad eller ett helt stadsområde, kan små justeringar skapa en betydande inverkan och förändra hur ett utrymme känns och fungerar. AAA:s tillvägagångssätt bygger på att lyssna och lära, för att skapa strategier och design som harmoniserar med omgivningen och svarar mot varje kunds unika behov.
-(I) AAA erbjuder stöd i att navigera, identifiera värden och hitta vägar framåt genom en [adaptiv metod i tidiga utvecklingsskeden](#/adaptive) för befintliga byggnader och platser. 
-(II) AAA har omfattande erfarenhet av [att leda arkitekturprojekt](#/architecture) för renoveringar eller tillägg, med målet att skapa största möjliga värde med de medel som finns tillgängliga.</t>
   </si>
   <si>
     <t>Grundade AAA 2024, tar med sig erfarenhet från Stockholm, Paris och Tokyo. Han har genomfört projekt från dialoger på plats till tidiga designförslag och till att följa genomförandet av bygget. Henrik undervisar vid Lunds universitet där han leder masterstudion Act of Altering och han är en aktiv röst i den pågående dialogen om den befintliga miljön och hållbarhet.</t>
@@ -401,24 +337,198 @@
     <t>Founded AAA 2024, bringing experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
   </si>
   <si>
-    <t>Clients: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
-Collaborations: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
-Presentations: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-Publications: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Aftonbladet](https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
-AAA is a Swedish shareholder company with the organisation number 556574-6152, formerly Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. All rights reserved.</t>
+    <t>artiklar länkar</t>
+  </si>
+  <si>
+    <t>https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**AAA works with renovations**, additions and strategies for the existing environment. Through the lens of an economic and technical know-how, weaved with ecological and cultural considerations, the present qualities are reinterpreted into a generous and functional space. </t>
+  </si>
+  <si>
+    <t>Through an adaptive approach we respond to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
+We are building for a new future, with the beautiful legacy from before us.</t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>plusTwo</t>
   </si>
   <si>
     <t>Kunder: [Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) och privat. 
 Samarbeten: [MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
 Presentationer: [Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
-Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Aftonbladet](https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).
-AAA är ett svenskt aktiebolag med organisationsnummer 556574-6152, tidigare Almquist Architecture Agency AB. © 2025 Agency for Adaptive Architecture. Alla rättigheter reserverade.</t>
+Publikationer: [Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Aftonbladet](https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).</t>
   </si>
   <si>
-    <t>artiklar länkar</t>
+    <t>**Impressum**</t>
   </si>
   <si>
-    <t>https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst</t>
+    <t>**Henrik Almquist, Arkitekt SAR/MSA, Dip. d’État France**</t>
+  </si>
+  <si>
+    <t>Agency for Adaptive Architecture AAA AB
+Östgötagatan 26, 116 25 Stockholm
+Organisation number 556574-6152
+VAT SE556574615201
+Email contact@a-a-a.se
+This website is operated and all content is owned by Agency for Adaptive Architecture AAA AB. © 2026 AAA. All rights reserved. Formerly Almquist Architecture Agency AB.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category:
+Place:  
+Year: 
+Client: 
+Use: 
+Size:
+Budget:
+Collaboration: 
+Team: </t>
+  </si>
+  <si>
+    <t>How can everyday environments inspire spatial thinking and use? What can be learned from the materials and spaces in our immediate surroundings? An ongoing photographic exploration of atmospheres and possibilities in existing settings. Here the photos are mixed with projects.</t>
+  </si>
+  <si>
+    <t>Everyday Qualities</t>
+  </si>
+  <si>
+    <t>AAA016</t>
+  </si>
+  <si>
+    <t>**Clients &amp; Collaborations**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
+[MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
+</t>
+  </si>
+  <si>
+    <t>[Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
+[Arkitektur](https://arkitektur.se/), [Rum](https://www.byrum.se/kategori/arkitektur/), [Arkitekten](https://arkitekten.se/), [Kritik](https://syntesforlag.blogspot.com/), [Aftonbladet](https://www.aftonbladet.se/debatt/a/0VKpxB/acan-sverige-fullt-fungerande-hus-rivs-i-jakt-pa-vinst), [Plan](https://www.planering.org/om-plan), [Utkast](http://faltstudio.com/).</t>
+  </si>
+  <si>
+    <t>plusone</t>
+  </si>
+  <si>
+    <t>**Presentations &amp; Publications**</t>
+  </si>
+  <si>
+    <t>Category: Competition
+Place:  Copenhagen
+Year: 2023
+Client: Art Fair Charlottenborg
+Use: Meeting pavilion
+Size: 15 sqm
+Budget:
+Collaboration: 
+Team: Morgane Martin-Alonzo, architect urbanist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category: Research
+Place: Malmö
+Year: 2020
+Client: MArch at ENSA Paris Malaquais
+Use: Development strategy Sofielund industrial area
+Size:
+Budget:
+Team: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category: Research on renovation
+Place:  Stockholm
+Year: 2023 - ongoing
+Funding: Riksbyggen, Tengbom &amp; AA Palmers
+Use: 
+Size:
+Budget:
+Team: </t>
+  </si>
+  <si>
+    <t>Category: Competition
+Place: Gothenburg
+Year: 2022
+Client: Gothenburg city
+Use: Kiosk
+Size: 18 sqm
+Budget:
+Team: Markus Gustafsson, architect engineer, Morgane Martin-Alonzo, architect urbanist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category: Renovation proposal
+Place:  Belo Horizonte
+Year: 2022 - 2024
+Client: Private
+Use: Residence
+Size: 300 sqm
+Budget:
+Team: </t>
+  </si>
+  <si>
+    <t>Category: Competition
+Place: Trondheim
+Year: 2023
+Client: 
+Use: Church
+Size: 1'400 sqm
+Budget:
+Team: Markus Gustafsson, architect engineer</t>
+  </si>
+  <si>
+    <t>AAA develops strategies and designs through listening and learning from the specific conditions of each project. Working within a wide and diverse network ensures that each project receives the right expertise and attention, whether taking on smaller projects or collaborating on larger and more complex ones.
+Phone: [+46793513461](tel:+46793513461)
+Mail: contact@a-a-a.se</t>
+  </si>
+  <si>
+    <t>Category: Competition honorable mention
+Place: Barcelona
+Year: 2024
+Client: City of Barcelona, Fundació Mies Van Der Rohe, UIA, UNESCO. 
+Use: Façade renovation and extension
+Size: 1'100 sqm
+Budget:
+Team: Josephine Harold, architect</t>
+  </si>
+  <si>
+    <t>Category: Competition 1st prize 
+Place: Växjö 
+Year: 2023 - ongoing
+Client: Växjö Municipality
+Use: Development and reuse strategy
+Size:
+Budget:
+Team: Morgane Martin-Alonzo, architect urbanist, Oscar Aparicio Chavez, architect, Léa Ganteil, architect reuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The renovated façade is animated by its new inhabitants; a rich biodiversity of deep soil, people opening up their apartments outside and natural integration of solar power production. A new language for the city of Barcelona marking an important entrance to the historic city and a park. 
+</t>
+  </si>
+  <si>
+    <t>The new church, surrounded by greenery, is a central part of Trondheim’s east. A large square in front creates space for activities and highlights the building. Its design combines a timeless main space with adaptable rooms. A green landscape wall creates a calm courtyard while reused materials, optimised space and design integrated solar panels ensure the building's longevity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The kiosk reacts differently to all of its sides, activating the public space by opening the shutters. I.e., offering a pause for the passer-by, protection for a short standing coffee, calmness for a seated meal or a quick take-away. The simple and economical wooden structure is built off site and lifted in place. The versatile design allows the building to adapt to many different uses, prolonging its longevity. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entering the courtyard all visitors are struck by the vivid activity in the space, a constantly changing landscape full of impressions. Built of reusable materials, the structure creates an open framework that gives space to what is already there to grow. The sound from the courtyard is recorded, delayed one day and then replayed in the interior acoustically separated room, offering a sort of collective memory. </t>
+  </si>
+  <si>
+    <t>Walls are moved, removed and added, finding new uses and enhancing dormant qualities of the building. The 1970s villa is opened up between the internal spaces as well as new openings excavated towards the outside. A room for meditation is extended in the back, offering a view of a new garden.</t>
+  </si>
+  <si>
+    <t>The way we work and live in the city is changing. Some buildings have a hard time adapting, especially offices from the 80s. What are their potential? How can we find new uses with simple interventions? Combining sustainability and economy, this research explores how current trends of renovation and demolition can evolve.</t>
+  </si>
+  <si>
+    <t>Centrally located in Växjö, the project explores what happens with the whole built environment if the hospital moves. We proposed a first phase with three interventions that help the city to understand how the existing structures can be reused, at the same time, mediating what citizens are expecting. The second phase is a hypothesis of what could be learned from the site and how that would take form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The project interacts with what already exists and proposes a solution of continuity. Acting on all the scales of the city, this project proposes a design approach of an active form. By defining a protocol, a new balance is expressed between the specificity of the local spaces/practices and the market driven urbanisation, while also giving form to an interstitial space that assures a temporality of use. </t>
   </si>
 </sst>
 </file>
@@ -827,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -847,15 +957,15 @@
     </row>
     <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -863,15 +973,15 @@
     </row>
     <row r="3" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -879,15 +989,15 @@
     </row>
     <row r="4" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3457,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -3477,15 +3587,15 @@
     </row>
     <row r="2" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6059,15 +6169,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753E04D3-4F26-42C1-99ED-EFD612322389}">
-  <dimension ref="A1:H268"/>
+  <dimension ref="A1:I268"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="5" width="40.6328125" customWidth="1"/>
-    <col min="6" max="6" width="47.6328125" customWidth="1"/>
-    <col min="7" max="8" width="10.6328125" customWidth="1"/>
+    <col min="2" max="6" width="40.6328125" customWidth="1"/>
+    <col min="7" max="7" width="47.6328125" customWidth="1"/>
+    <col min="8" max="9" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6075,25 +6185,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -6104,22 +6217,25 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>0.15</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -6130,204 +6246,228 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="145" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2">
         <v>0.15</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I4" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="145" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="2">
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="2">
         <v>0.15</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="145" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I8" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2">
+    <row r="9" spans="1:9" ht="174" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="2">
         <v>0.15</v>
       </c>
-      <c r="H5" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="H6" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="H7" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="145" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="I9" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:9" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -6336,8 +6476,9 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -6346,8 +6487,9 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -6356,8 +6498,9 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -6366,8 +6509,9 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -6376,8 +6520,9 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -6386,8 +6531,9 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -6396,8 +6542,9 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -6406,8 +6553,9 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -6416,8 +6564,9 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -6426,8 +6575,9 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -6436,8 +6586,9 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -6446,8 +6597,9 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -6456,8 +6608,9 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -6466,8 +6619,9 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -6476,8 +6630,9 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -6486,8 +6641,9 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -6496,8 +6652,9 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -6506,8 +6663,9 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -6516,8 +6674,9 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -6526,8 +6685,9 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -6536,8 +6696,9 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -6546,8 +6707,9 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -6556,8 +6718,9 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -6566,8 +6729,9 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -6576,8 +6740,9 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -6586,8 +6751,9 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -6596,8 +6762,9 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -6606,8 +6773,9 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -6616,8 +6784,9 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -6626,8 +6795,9 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -6636,8 +6806,9 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -6646,8 +6817,9 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -6656,8 +6828,9 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -6666,8 +6839,9 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -6676,8 +6850,9 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -6686,8 +6861,9 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6696,8 +6872,9 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -6706,8 +6883,9 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -6716,8 +6894,9 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -6726,8 +6905,9 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -6736,8 +6916,9 @@
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -6746,8 +6927,9 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -6756,8 +6938,9 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -6766,8 +6949,9 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -6776,8 +6960,9 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -6786,8 +6971,9 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -6796,8 +6982,9 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -6806,8 +6993,9 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -6816,8 +7004,9 @@
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -6826,8 +7015,9 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -6836,8 +7026,9 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -6846,8 +7037,9 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -6856,8 +7048,9 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -6866,8 +7059,9 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -6876,8 +7070,9 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -6886,8 +7081,9 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -6896,8 +7092,9 @@
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -6906,8 +7103,9 @@
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -6916,8 +7114,9 @@
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -6926,8 +7125,9 @@
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -6936,8 +7136,9 @@
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -6946,8 +7147,9 @@
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -6956,8 +7158,9 @@
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -6966,8 +7169,9 @@
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -6976,8 +7180,9 @@
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -6986,8 +7191,9 @@
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -6996,8 +7202,9 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -7006,8 +7213,9 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -7016,8 +7224,9 @@
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I79" s="2"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -7026,8 +7235,9 @@
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I80" s="2"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -7036,8 +7246,9 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I81" s="2"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -7046,8 +7257,9 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I82" s="2"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -7056,8 +7268,9 @@
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -7066,8 +7279,9 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I84" s="2"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -7076,8 +7290,9 @@
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I85" s="2"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -7086,8 +7301,9 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I86" s="2"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -7096,8 +7312,9 @@
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I87" s="2"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -7106,8 +7323,9 @@
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I88" s="2"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -7116,8 +7334,9 @@
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I89" s="2"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -7126,8 +7345,9 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I90" s="2"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -7136,8 +7356,9 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I91" s="2"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -7146,8 +7367,9 @@
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I92" s="2"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -7156,8 +7378,9 @@
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I93" s="2"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -7166,8 +7389,9 @@
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I94" s="2"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -7176,8 +7400,9 @@
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I95" s="2"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -7186,8 +7411,9 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I96" s="2"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -7196,8 +7422,9 @@
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I97" s="2"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -7206,8 +7433,9 @@
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I98" s="2"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -7216,8 +7444,9 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I99" s="2"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -7226,8 +7455,9 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I100" s="2"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -7236,8 +7466,9 @@
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I101" s="2"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -7246,8 +7477,9 @@
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I102" s="2"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -7256,8 +7488,9 @@
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I103" s="2"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -7266,8 +7499,9 @@
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I104" s="2"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -7276,8 +7510,9 @@
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I105" s="2"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -7286,8 +7521,9 @@
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I106" s="2"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -7296,8 +7532,9 @@
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I107" s="2"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -7306,8 +7543,9 @@
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I108" s="2"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -7316,8 +7554,9 @@
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I109" s="2"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -7326,8 +7565,9 @@
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I110" s="2"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -7336,8 +7576,9 @@
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I111" s="2"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -7346,8 +7587,9 @@
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I112" s="2"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -7356,8 +7598,9 @@
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I113" s="2"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -7366,8 +7609,9 @@
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I114" s="2"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -7376,8 +7620,9 @@
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I115" s="2"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -7386,8 +7631,9 @@
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I116" s="2"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -7396,8 +7642,9 @@
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I117" s="2"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -7406,8 +7653,9 @@
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I118" s="2"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -7416,8 +7664,9 @@
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I119" s="2"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -7426,8 +7675,9 @@
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I120" s="2"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -7436,8 +7686,9 @@
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I121" s="2"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -7446,8 +7697,9 @@
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I122" s="2"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -7456,8 +7708,9 @@
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I123" s="2"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -7466,8 +7719,9 @@
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I124" s="2"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -7476,8 +7730,9 @@
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I125" s="2"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -7486,8 +7741,9 @@
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I126" s="2"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -7496,8 +7752,9 @@
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I127" s="2"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -7506,8 +7763,9 @@
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I128" s="2"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -7516,8 +7774,9 @@
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I129" s="2"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -7526,8 +7785,9 @@
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I130" s="2"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -7536,8 +7796,9 @@
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I131" s="2"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -7546,8 +7807,9 @@
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I132" s="2"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -7556,8 +7818,9 @@
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I133" s="2"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -7566,8 +7829,9 @@
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I134" s="2"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -7576,8 +7840,9 @@
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I135" s="2"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -7586,8 +7851,9 @@
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I136" s="2"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -7596,8 +7862,9 @@
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I137" s="2"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -7606,8 +7873,9 @@
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I138" s="2"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -7616,8 +7884,9 @@
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I139" s="2"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -7626,8 +7895,9 @@
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I140" s="2"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -7636,8 +7906,9 @@
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I141" s="2"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -7646,8 +7917,9 @@
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I142" s="2"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -7656,8 +7928,9 @@
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I143" s="2"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -7666,8 +7939,9 @@
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I144" s="2"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -7676,8 +7950,9 @@
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I145" s="2"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -7686,8 +7961,9 @@
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I146" s="2"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -7696,8 +7972,9 @@
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I147" s="2"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -7706,8 +7983,9 @@
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I148" s="2"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -7716,8 +7994,9 @@
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I149" s="2"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -7726,8 +8005,9 @@
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I150" s="2"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -7736,8 +8016,9 @@
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I151" s="2"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -7746,8 +8027,9 @@
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I152" s="2"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -7756,8 +8038,9 @@
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I153" s="2"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -7766,8 +8049,9 @@
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I154" s="2"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -7776,8 +8060,9 @@
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I155" s="2"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -7786,8 +8071,9 @@
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I156" s="2"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -7796,8 +8082,9 @@
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I157" s="2"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -7806,8 +8093,9 @@
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I158" s="2"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -7816,8 +8104,9 @@
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I159" s="2"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -7826,8 +8115,9 @@
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I160" s="2"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -7836,8 +8126,9 @@
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I161" s="2"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -7846,8 +8137,9 @@
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I162" s="2"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -7856,8 +8148,9 @@
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I163" s="2"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -7866,8 +8159,9 @@
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I164" s="2"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -7876,8 +8170,9 @@
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I165" s="2"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -7886,8 +8181,9 @@
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I166" s="2"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -7896,8 +8192,9 @@
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I167" s="2"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -7906,8 +8203,9 @@
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I168" s="2"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -7916,8 +8214,9 @@
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I169" s="2"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -7926,8 +8225,9 @@
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I170" s="2"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -7936,8 +8236,9 @@
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I171" s="2"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -7946,8 +8247,9 @@
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I172" s="2"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -7956,8 +8258,9 @@
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I173" s="2"/>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -7966,8 +8269,9 @@
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I174" s="2"/>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -7976,8 +8280,9 @@
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I175" s="2"/>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -7986,8 +8291,9 @@
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I176" s="2"/>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -7996,8 +8302,9 @@
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I177" s="2"/>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -8006,8 +8313,9 @@
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I178" s="2"/>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -8016,8 +8324,9 @@
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I179" s="2"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -8026,8 +8335,9 @@
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I180" s="2"/>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -8036,8 +8346,9 @@
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I181" s="2"/>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -8046,8 +8357,9 @@
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I182" s="2"/>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -8056,8 +8368,9 @@
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I183" s="2"/>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -8066,8 +8379,9 @@
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I184" s="2"/>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -8076,8 +8390,9 @@
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I185" s="2"/>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -8086,8 +8401,9 @@
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I186" s="2"/>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -8096,8 +8412,9 @@
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I187" s="2"/>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -8106,8 +8423,9 @@
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I188" s="2"/>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -8116,8 +8434,9 @@
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I189" s="2"/>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -8126,8 +8445,9 @@
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I190" s="2"/>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -8136,8 +8456,9 @@
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I191" s="2"/>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -8146,8 +8467,9 @@
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I192" s="2"/>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -8156,8 +8478,9 @@
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I193" s="2"/>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -8166,8 +8489,9 @@
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I194" s="2"/>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -8176,8 +8500,9 @@
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I195" s="2"/>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -8186,8 +8511,9 @@
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I196" s="2"/>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -8196,8 +8522,9 @@
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I197" s="2"/>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -8206,8 +8533,9 @@
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I198" s="2"/>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -8216,8 +8544,9 @@
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I199" s="2"/>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -8226,8 +8555,9 @@
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I200" s="2"/>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -8236,8 +8566,9 @@
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I201" s="2"/>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -8246,8 +8577,9 @@
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I202" s="2"/>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -8256,8 +8588,9 @@
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I203" s="2"/>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -8266,8 +8599,9 @@
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I204" s="2"/>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -8276,8 +8610,9 @@
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I205" s="2"/>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -8286,8 +8621,9 @@
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I206" s="2"/>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -8296,8 +8632,9 @@
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I207" s="2"/>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -8306,8 +8643,9 @@
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I208" s="2"/>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -8316,8 +8654,9 @@
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I209" s="2"/>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -8326,8 +8665,9 @@
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I210" s="2"/>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -8336,8 +8676,9 @@
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I211" s="2"/>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -8346,8 +8687,9 @@
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I212" s="2"/>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -8356,8 +8698,9 @@
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I213" s="2"/>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -8366,8 +8709,9 @@
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I214" s="2"/>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -8376,8 +8720,9 @@
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I215" s="2"/>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -8386,8 +8731,9 @@
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I216" s="2"/>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -8396,8 +8742,9 @@
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I217" s="2"/>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -8406,8 +8753,9 @@
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I218" s="2"/>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -8416,8 +8764,9 @@
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I219" s="2"/>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -8426,8 +8775,9 @@
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I220" s="2"/>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -8436,8 +8786,9 @@
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I221" s="2"/>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -8446,8 +8797,9 @@
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I222" s="2"/>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -8456,8 +8808,9 @@
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I223" s="2"/>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -8466,8 +8819,9 @@
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I224" s="2"/>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -8476,8 +8830,9 @@
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I225" s="2"/>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -8486,8 +8841,9 @@
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I226" s="2"/>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -8496,8 +8852,9 @@
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I227" s="2"/>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -8506,8 +8863,9 @@
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I228" s="2"/>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -8516,8 +8874,9 @@
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I229" s="2"/>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -8526,8 +8885,9 @@
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I230" s="2"/>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -8536,8 +8896,9 @@
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I231" s="2"/>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -8546,8 +8907,9 @@
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I232" s="2"/>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -8556,8 +8918,9 @@
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I233" s="2"/>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -8566,8 +8929,9 @@
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I234" s="2"/>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -8576,8 +8940,9 @@
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I235" s="2"/>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -8586,8 +8951,9 @@
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I236" s="2"/>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -8596,8 +8962,9 @@
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I237" s="2"/>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -8606,8 +8973,9 @@
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I238" s="2"/>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -8616,8 +8984,9 @@
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I239" s="2"/>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -8626,8 +8995,9 @@
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I240" s="2"/>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -8636,8 +9006,9 @@
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I241" s="2"/>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -8646,8 +9017,9 @@
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I242" s="2"/>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -8656,8 +9028,9 @@
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I243" s="2"/>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -8666,8 +9039,9 @@
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I244" s="2"/>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -8676,8 +9050,9 @@
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I245" s="2"/>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -8686,8 +9061,9 @@
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I246" s="2"/>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -8696,8 +9072,9 @@
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I247" s="2"/>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -8706,8 +9083,9 @@
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I248" s="2"/>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -8716,8 +9094,9 @@
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I249" s="2"/>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -8726,8 +9105,9 @@
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I250" s="2"/>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -8736,8 +9116,9 @@
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I251" s="2"/>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -8746,8 +9127,9 @@
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I252" s="2"/>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -8756,8 +9138,9 @@
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I253" s="2"/>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -8766,8 +9149,9 @@
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I254" s="2"/>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -8776,8 +9160,9 @@
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I255" s="2"/>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -8786,8 +9171,9 @@
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I256" s="2"/>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -8796,8 +9182,9 @@
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I257" s="2"/>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -8806,8 +9193,9 @@
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I258" s="2"/>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -8816,8 +9204,9 @@
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I259" s="2"/>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -8826,8 +9215,9 @@
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I260" s="2"/>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -8836,8 +9226,9 @@
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I261" s="2"/>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -8846,8 +9237,9 @@
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I262" s="2"/>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -8856,8 +9248,9 @@
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I263" s="2"/>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -8866,8 +9259,9 @@
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I264" s="2"/>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -8876,8 +9270,9 @@
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I265" s="2"/>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -8886,8 +9281,9 @@
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I266" s="2"/>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -8896,8 +9292,9 @@
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I267" s="2"/>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -8906,6 +9303,7 @@
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
+      <c r="I268" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8929,7 +9327,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -8951,13 +9349,13 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -8966,19 +9364,19 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -8989,19 +9387,19 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -9012,19 +9410,19 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -11404,136 +11802,167 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04093925-E5E8-4C20-AF94-7ABD304FA7F3}">
-  <dimension ref="A1:G269"/>
+  <dimension ref="A1:H270"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.6328125" customWidth="1"/>
-    <col min="2" max="3" width="40.6328125" customWidth="1"/>
-    <col min="4" max="4" width="65.90625" customWidth="1"/>
-    <col min="5" max="5" width="68.81640625" customWidth="1"/>
-    <col min="6" max="7" width="40.6328125" customWidth="1"/>
+    <col min="1" max="2" width="13.6328125" customWidth="1"/>
+    <col min="3" max="4" width="40.6328125" customWidth="1"/>
+    <col min="5" max="5" width="65.90625" customWidth="1"/>
+    <col min="6" max="6" width="68.81640625" customWidth="1"/>
+    <col min="7" max="8" width="40.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="203" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="2">
+        <v>78</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -11541,8 +11970,9 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -11550,8 +11980,9 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -11559,8 +11990,9 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -11568,30 +12000,33 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>104</v>
-      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -11599,8 +12034,9 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -11608,8 +12044,9 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -11617,8 +12054,9 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -11626,8 +12064,9 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -11635,8 +12074,9 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -11644,8 +12084,9 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -11653,8 +12094,9 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -11662,8 +12104,9 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -11671,8 +12114,9 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -11680,8 +12124,9 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -11689,8 +12134,9 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -11698,8 +12144,9 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -11707,8 +12154,9 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -11716,8 +12164,9 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -11725,8 +12174,9 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -11734,8 +12184,9 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -11743,8 +12194,9 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -11752,8 +12204,9 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -11761,8 +12214,9 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -11770,8 +12224,9 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -11779,8 +12234,9 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -11788,8 +12244,9 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -11797,8 +12254,9 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -11806,8 +12264,9 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -11815,8 +12274,9 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -11824,8 +12284,9 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -11833,8 +12294,9 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -11842,8 +12304,9 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -11851,8 +12314,9 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -11860,8 +12324,9 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -11869,8 +12334,9 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -11878,8 +12344,9 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -11887,8 +12354,9 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -11896,8 +12364,9 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -11905,8 +12374,9 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -11914,8 +12384,9 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -11923,8 +12394,9 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -11932,8 +12404,9 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -11941,8 +12414,9 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -11950,8 +12424,9 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -11959,8 +12434,9 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -11968,8 +12444,9 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -11977,8 +12454,9 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -11986,8 +12464,9 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -11995,8 +12474,9 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -12004,8 +12484,9 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -12013,8 +12494,9 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -12022,8 +12504,9 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -12031,8 +12514,9 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -12040,8 +12524,9 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -12049,8 +12534,9 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -12058,8 +12544,9 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -12067,8 +12554,9 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -12076,8 +12564,9 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -12085,8 +12574,9 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -12094,8 +12584,9 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -12103,8 +12594,9 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -12112,8 +12604,9 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -12121,8 +12614,9 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -12130,8 +12624,9 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -12139,8 +12634,9 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -12148,8 +12644,9 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -12157,8 +12654,9 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -12166,8 +12664,9 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -12175,8 +12674,9 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -12184,8 +12684,9 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -12193,8 +12694,9 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -12202,8 +12704,9 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -12211,8 +12714,9 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -12220,8 +12724,9 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -12229,8 +12734,9 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -12238,8 +12744,9 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -12247,8 +12754,9 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -12256,8 +12764,9 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -12265,8 +12774,9 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -12274,8 +12784,9 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -12283,8 +12794,9 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -12292,8 +12804,9 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -12301,8 +12814,9 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -12310,8 +12824,9 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -12319,8 +12834,9 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -12328,8 +12844,9 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -12337,8 +12854,9 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -12346,8 +12864,9 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H97" s="2"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -12355,8 +12874,9 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -12364,8 +12884,9 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -12373,8 +12894,9 @@
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H100" s="2"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -12382,8 +12904,9 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H101" s="2"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -12391,8 +12914,9 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H102" s="2"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -12400,8 +12924,9 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H103" s="2"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -12409,8 +12934,9 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -12418,8 +12944,9 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H105" s="2"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -12427,8 +12954,9 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -12436,8 +12964,9 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H107" s="2"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -12445,8 +12974,9 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H108" s="2"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -12454,8 +12984,9 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H109" s="2"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -12463,8 +12994,9 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H110" s="2"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -12472,8 +13004,9 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H111" s="2"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -12481,8 +13014,9 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H112" s="2"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -12490,8 +13024,9 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H113" s="2"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -12499,8 +13034,9 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H114" s="2"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -12508,8 +13044,9 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H115" s="2"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -12517,8 +13054,9 @@
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H116" s="2"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -12526,8 +13064,9 @@
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H117" s="2"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -12535,8 +13074,9 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H118" s="2"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -12544,8 +13084,9 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H119" s="2"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -12553,8 +13094,9 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H120" s="2"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -12562,8 +13104,9 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H121" s="2"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -12571,8 +13114,9 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H122" s="2"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -12580,8 +13124,9 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H123" s="2"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -12589,8 +13134,9 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H124" s="2"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -12598,8 +13144,9 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H125" s="2"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -12607,8 +13154,9 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H126" s="2"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -12616,8 +13164,9 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H127" s="2"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -12625,8 +13174,9 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H128" s="2"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -12634,8 +13184,9 @@
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H129" s="2"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -12643,8 +13194,9 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H130" s="2"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -12652,8 +13204,9 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H131" s="2"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -12661,8 +13214,9 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H132" s="2"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -12670,8 +13224,9 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H133" s="2"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -12679,8 +13234,9 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H134" s="2"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -12688,8 +13244,9 @@
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H135" s="2"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -12697,8 +13254,9 @@
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H136" s="2"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -12706,8 +13264,9 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H137" s="2"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -12715,8 +13274,9 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H138" s="2"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -12724,8 +13284,9 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H139" s="2"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -12733,8 +13294,9 @@
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H140" s="2"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -12742,8 +13304,9 @@
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H141" s="2"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -12751,8 +13314,9 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H142" s="2"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -12760,8 +13324,9 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H143" s="2"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -12769,8 +13334,9 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H144" s="2"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -12778,8 +13344,9 @@
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H145" s="2"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -12787,8 +13354,9 @@
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H146" s="2"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -12796,8 +13364,9 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H147" s="2"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -12805,8 +13374,9 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H148" s="2"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -12814,8 +13384,9 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H149" s="2"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -12823,8 +13394,9 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H150" s="2"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -12832,8 +13404,9 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H151" s="2"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -12841,8 +13414,9 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H152" s="2"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -12850,8 +13424,9 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H153" s="2"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -12859,8 +13434,9 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H154" s="2"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -12868,8 +13444,9 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H155" s="2"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -12877,8 +13454,9 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H156" s="2"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -12886,8 +13464,9 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H157" s="2"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -12895,8 +13474,9 @@
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H158" s="2"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -12904,8 +13484,9 @@
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H159" s="2"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -12913,8 +13494,9 @@
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H160" s="2"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -12922,8 +13504,9 @@
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H161" s="2"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -12931,8 +13514,9 @@
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H162" s="2"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -12940,8 +13524,9 @@
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H163" s="2"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -12949,8 +13534,9 @@
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H164" s="2"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -12958,8 +13544,9 @@
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H165" s="2"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -12967,8 +13554,9 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H166" s="2"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -12976,8 +13564,9 @@
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H167" s="2"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -12985,8 +13574,9 @@
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H168" s="2"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -12994,8 +13584,9 @@
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H169" s="2"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -13003,8 +13594,9 @@
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H170" s="2"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -13012,8 +13604,9 @@
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H171" s="2"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -13021,8 +13614,9 @@
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H172" s="2"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -13030,8 +13624,9 @@
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H173" s="2"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -13039,8 +13634,9 @@
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H174" s="2"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -13048,8 +13644,9 @@
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H175" s="2"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -13057,8 +13654,9 @@
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H176" s="2"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -13066,8 +13664,9 @@
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H177" s="2"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -13075,8 +13674,9 @@
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H178" s="2"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -13084,8 +13684,9 @@
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H179" s="2"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -13093,8 +13694,9 @@
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H180" s="2"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -13102,8 +13704,9 @@
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H181" s="2"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -13111,8 +13714,9 @@
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H182" s="2"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -13120,8 +13724,9 @@
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H183" s="2"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -13129,8 +13734,9 @@
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H184" s="2"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -13138,8 +13744,9 @@
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H185" s="2"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -13147,8 +13754,9 @@
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H186" s="2"/>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -13156,8 +13764,9 @@
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H187" s="2"/>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -13165,8 +13774,9 @@
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H188" s="2"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -13174,8 +13784,9 @@
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H189" s="2"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -13183,8 +13794,9 @@
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H190" s="2"/>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -13192,8 +13804,9 @@
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H191" s="2"/>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -13201,8 +13814,9 @@
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H192" s="2"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -13210,8 +13824,9 @@
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H193" s="2"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -13219,8 +13834,9 @@
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H194" s="2"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -13228,8 +13844,9 @@
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H195" s="2"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -13237,8 +13854,9 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H196" s="2"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -13246,8 +13864,9 @@
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H197" s="2"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -13255,8 +13874,9 @@
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H198" s="2"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -13264,8 +13884,9 @@
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H199" s="2"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -13273,8 +13894,9 @@
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H200" s="2"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -13282,8 +13904,9 @@
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H201" s="2"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -13291,8 +13914,9 @@
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H202" s="2"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -13300,8 +13924,9 @@
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H203" s="2"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -13309,8 +13934,9 @@
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H204" s="2"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -13318,8 +13944,9 @@
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H205" s="2"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -13327,8 +13954,9 @@
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H206" s="2"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -13336,8 +13964,9 @@
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H207" s="2"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -13345,8 +13974,9 @@
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H208" s="2"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -13354,8 +13984,9 @@
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H209" s="2"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -13363,8 +13994,9 @@
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H210" s="2"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -13372,8 +14004,9 @@
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H211" s="2"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -13381,8 +14014,9 @@
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H212" s="2"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -13390,8 +14024,9 @@
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H213" s="2"/>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -13399,8 +14034,9 @@
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H214" s="2"/>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -13408,8 +14044,9 @@
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H215" s="2"/>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -13417,8 +14054,9 @@
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H216" s="2"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -13426,8 +14064,9 @@
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H217" s="2"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -13435,8 +14074,9 @@
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H218" s="2"/>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -13444,8 +14084,9 @@
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H219" s="2"/>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -13453,8 +14094,9 @@
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H220" s="2"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -13462,8 +14104,9 @@
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H221" s="2"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -13471,8 +14114,9 @@
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H222" s="2"/>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -13480,8 +14124,9 @@
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H223" s="2"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -13489,8 +14134,9 @@
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H224" s="2"/>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -13498,8 +14144,9 @@
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H225" s="2"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -13507,8 +14154,9 @@
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H226" s="2"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -13516,8 +14164,9 @@
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H227" s="2"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -13525,8 +14174,9 @@
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H228" s="2"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -13534,8 +14184,9 @@
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H229" s="2"/>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -13543,8 +14194,9 @@
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H230" s="2"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -13552,8 +14204,9 @@
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H231" s="2"/>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -13561,8 +14214,9 @@
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H232" s="2"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -13570,8 +14224,9 @@
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H233" s="2"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -13579,8 +14234,9 @@
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H234" s="2"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -13588,8 +14244,9 @@
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H235" s="2"/>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -13597,8 +14254,9 @@
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H236" s="2"/>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -13606,8 +14264,9 @@
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H237" s="2"/>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -13615,8 +14274,9 @@
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H238" s="2"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -13624,8 +14284,9 @@
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H239" s="2"/>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -13633,8 +14294,9 @@
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H240" s="2"/>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -13642,8 +14304,9 @@
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H241" s="2"/>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -13651,8 +14314,9 @@
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H242" s="2"/>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -13660,8 +14324,9 @@
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H243" s="2"/>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -13669,8 +14334,9 @@
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H244" s="2"/>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -13678,8 +14344,9 @@
       <c r="E245" s="2"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H245" s="2"/>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -13687,8 +14354,9 @@
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H246" s="2"/>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -13696,8 +14364,9 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H247" s="2"/>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -13705,8 +14374,9 @@
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H248" s="2"/>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -13714,8 +14384,9 @@
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H249" s="2"/>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -13723,8 +14394,9 @@
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H250" s="2"/>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -13732,8 +14404,9 @@
       <c r="E251" s="2"/>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H251" s="2"/>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -13741,8 +14414,9 @@
       <c r="E252" s="2"/>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H252" s="2"/>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -13750,8 +14424,9 @@
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H253" s="2"/>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -13759,8 +14434,9 @@
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H254" s="2"/>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -13768,8 +14444,9 @@
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H255" s="2"/>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -13777,8 +14454,9 @@
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H256" s="2"/>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -13786,8 +14464,9 @@
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H257" s="2"/>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -13795,8 +14474,9 @@
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H258" s="2"/>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -13804,8 +14484,9 @@
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H259" s="2"/>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -13813,8 +14494,9 @@
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H260" s="2"/>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -13822,8 +14504,9 @@
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H261" s="2"/>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -13831,8 +14514,9 @@
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H262" s="2"/>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -13840,8 +14524,9 @@
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H263" s="2"/>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -13849,8 +14534,9 @@
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H264" s="2"/>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -13858,8 +14544,9 @@
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H265" s="2"/>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -13867,8 +14554,9 @@
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H266" s="2"/>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -13876,8 +14564,9 @@
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H267" s="2"/>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -13885,8 +14574,9 @@
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H268" s="2"/>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -13894,6 +14584,17 @@
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
+      <c r="H269" s="2"/>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A270" s="2"/>
+      <c r="B270" s="2"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
+      <c r="E270" s="2"/>
+      <c r="F270" s="2"/>
+      <c r="G270" s="2"/>
+      <c r="H270" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95333698-08D9-441C-9649-CF09E5FBD1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABD3A5C-E5F6-436A-B464-583861D66500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="3" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>AAA019</t>
-  </si>
-  <si>
-    <t>Generative Care, 1e Prize</t>
   </si>
   <si>
     <t>AAA024</t>
@@ -346,10 +343,6 @@
     <t xml:space="preserve">**AAA works with renovations**, additions and strategies for the existing environment. Through the lens of an economic and technical know-how, weaved with ecological and cultural considerations, the present qualities are reinterpreted into a generous and functional space. </t>
   </si>
   <si>
-    <t>Through an adaptive approach we respond to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
-We are building for a new future, with the beautiful legacy from before us.</t>
-  </si>
-  <si>
     <t>Meta</t>
   </si>
   <si>
@@ -529,6 +522,13 @@
   </si>
   <si>
     <t xml:space="preserve">The project interacts with what already exists and proposes a solution of continuity. Acting on all the scales of the city, this project proposes a design approach of an active form. By defining a protocol, a new balance is expressed between the specificity of the local spaces/practices and the market driven urbanisation, while also giving form to an interstitial space that assures a temporality of use. </t>
+  </si>
+  <si>
+    <t>Generative Care 1e Prize</t>
+  </si>
+  <si>
+    <t>Through an adaptive approach AAA respond to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
+We are building for a new future, with the beautiful legacy from before us.</t>
   </si>
 </sst>
 </file>
@@ -931,13 +931,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -946,26 +946,26 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -973,15 +973,15 @@
     </row>
     <row r="3" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -989,15 +989,15 @@
     </row>
     <row r="4" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3561,13 +3561,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -3576,26 +3576,26 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -6185,10 +6185,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -6197,13 +6197,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
@@ -6211,22 +6211,22 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2">
         <v>0.15</v>
@@ -6237,25 +6237,25 @@
     </row>
     <row r="3" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2">
         <v>0.15</v>
@@ -6266,25 +6266,25 @@
     </row>
     <row r="4" spans="1:9" ht="145" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2">
         <v>0.15</v>
@@ -6295,25 +6295,25 @@
     </row>
     <row r="5" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5" s="2">
         <v>0.15</v>
@@ -6324,25 +6324,25 @@
     </row>
     <row r="6" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2">
         <v>0.15</v>
@@ -6353,25 +6353,25 @@
     </row>
     <row r="7" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2">
         <v>0.15</v>
@@ -6382,25 +6382,25 @@
     </row>
     <row r="8" spans="1:9" ht="145" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2">
         <v>0.15</v>
@@ -6411,25 +6411,25 @@
     </row>
     <row r="9" spans="1:9" ht="174" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H9" s="2">
         <v>0.15</v>
@@ -6440,25 +6440,25 @@
     </row>
     <row r="10" spans="1:9" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -9321,13 +9321,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -9336,47 +9336,47 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="174" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -9384,22 +9384,22 @@
     </row>
     <row r="4" spans="1:7" ht="232" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -9407,22 +9407,22 @@
     </row>
     <row r="5" spans="1:7" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -11814,16 +11814,16 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -11832,51 +11832,51 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -11884,7 +11884,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -11896,22 +11896,22 @@
     </row>
     <row r="5" spans="1:8" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2">
@@ -11920,17 +11920,17 @@
     </row>
     <row r="6" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -11940,22 +11940,22 @@
     </row>
     <row r="7" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2">
@@ -12014,11 +12014,11 @@
     </row>
     <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABD3A5C-E5F6-436A-B464-583861D66500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD3A8D7-310F-4992-A397-48694F6B6DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="3" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -331,9 +331,6 @@
 **Att navigera i denna skärningspunkt mellan ekonomi och ekologi, kultur och teknik, är AAA:s expertis.**</t>
   </si>
   <si>
-    <t>Founded AAA 2024, bringing experience from Stockholm, Paris and Tokyo. He has carried out projects from  in-situ dialogues to early design proposals to seeing through the construction. Henrik teaches at Lund University where he directs the masterstudio Act of Altering and he is an active voice in the ongoing dialogue on the existing environment and sustainability.</t>
-  </si>
-  <si>
     <t>artiklar länkar</t>
   </si>
   <si>
@@ -396,11 +393,6 @@
   </si>
   <si>
     <t>**Clients &amp; Collaborations**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](malmö.se) and private. 
-[MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingård Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Rambøll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö universitet](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
-</t>
   </si>
   <si>
     <t>[Form Design Center Skåne](https://formdesigncenter.com/), [TU Graz](https://www.tugraz.at/en/fakultaeten/architektur/home), [Krook &amp; Tjäder Arkitekter](http://www.krook.tjader.se/), [Sällskapet för restaurering](https://sallskapet.eu/). 
@@ -474,11 +466,6 @@
 Team: Markus Gustafsson, architect engineer</t>
   </si>
   <si>
-    <t>AAA develops strategies and designs through listening and learning from the specific conditions of each project. Working within a wide and diverse network ensures that each project receives the right expertise and attention, whether taking on smaller projects or collaborating on larger and more complex ones.
-Phone: [+46793513461](tel:+46793513461)
-Mail: contact@a-a-a.se</t>
-  </si>
-  <si>
     <t>Category: Competition honorable mention
 Place: Barcelona
 Year: 2024
@@ -527,8 +514,22 @@
     <t>Generative Care 1e Prize</t>
   </si>
   <si>
-    <t>Through an adaptive approach AAA respond to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
-We are building for a new future, with the beautiful legacy from before us.</t>
+    <t xml:space="preserve">[Riksbyggen](https://www.riksbyggen.se), [Lund City](https://en.lundcity.se/), [Växjö Municipality](https://www.vaxjo.se/), [The Ministry for Europe and Foreign Affairs France](https://www.diplomatie.gouv.fr/en/), [Malmö Stad](https://malmo.se) and private clients. 
+[MOD Group](https://www.modgroup.se/), [Draken Arkitektur](https://drakenarkitektur.se/), [Outer Space Landscape Architecture](https://outerspacearkitekter.se/), [Blick Arkitektur](https://www.blickarkitektur.se/), [Wingårdhs Arkitektkontor](https://www.wingardhs.se), [LTH](https://www.arch.lth.se/), [KTH](https://www.kth.se/en/abe), [Ramboll Group](https://www.ramboll.com/), [Djernes &amp; Bell](https://djernesbell.com/en), [Grip+Torarp](https://www.griptorarp.com/), [Malmö University](https://mau.se/forskning/forskningsamnen/urbana-studier/), [Contexo Studio](https://www.contexo.studio/), [Studio 1836](https://www.studio1836.fr/).
+</t>
+  </si>
+  <si>
+    <t>Through an adaptive approach AAA responds to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
+We are building for a new future, with the beautiful legacy that came before us.</t>
+  </si>
+  <si>
+    <t>Before founding AAA in 2024, Henrik Almquist gained experience at Arrhov Frick in Stockholm, Studio Muoto and Sou Fujimoto in Paris. He has carried out projects ranging from in-situ dialogues and early design proposals to overseeing construction. Henrik teaches at Lund University, where he directs the master studio Act of Altering on preservation and renovation. He is an active voice in the public dialogue on the existing built environment and sustainability.</t>
+  </si>
+  <si>
+    <t>AAA develops strategies and designs by listening and learning from the specific conditions of each project. Working within a wide and diverse network ensures that each project receives the right expertise and attention, whether taking on smaller projects or collaborating on larger and more complex ones.
+In 2023 AAA won the competition for a reuse and development strategy for the Växjö hospital area. Current work includes renovation projects and an early phase study with Riksbyggen. Research funded by ARQ develops methods to identify existing values and adaptation potential in buildings.
+Phone: [+46793513461](tel:+46793513461)
+Email: contact@a-a-a.se</t>
   </si>
 </sst>
 </file>
@@ -3592,7 +3593,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>63</v>
@@ -6188,7 +6189,7 @@
         <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -6211,16 +6212,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>54</v>
@@ -6246,10 +6247,10 @@
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>43</v>
@@ -6275,10 +6276,10 @@
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>55</v>
@@ -6304,10 +6305,10 @@
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>56</v>
@@ -6333,10 +6334,10 @@
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>61</v>
@@ -6362,10 +6363,10 @@
         <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>57</v>
@@ -6391,10 +6392,10 @@
         <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>62</v>
@@ -6420,10 +6421,10 @@
         <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>58</v>
@@ -6440,19 +6441,19 @@
     </row>
     <row r="10" spans="1:9" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>59</v>
@@ -9349,7 +9350,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>67</v>
@@ -11838,7 +11839,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -11846,7 +11847,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>75</v>
@@ -11856,21 +11857,21 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
@@ -11899,19 +11900,19 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2">
@@ -11920,17 +11921,17 @@
     </row>
     <row r="6" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -11940,22 +11941,22 @@
     </row>
     <row r="7" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2">
@@ -12014,11 +12015,11 @@
     </row>
     <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD3A8D7-310F-4992-A397-48694F6B6DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F4C562-61AC-4236-818E-7DC6348EB5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="4" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -277,10 +277,6 @@
     <t>AAA000/Almquist_Form-Design-Center-Malmo_w.jpg</t>
   </si>
   <si>
-    <t>The richness inherited is often irreplaceable. Materials and elaborate craftmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
-Qualities we so often try to recreate are already present, waiting to be cared for, adapted and brought into new use.</t>
-  </si>
-  <si>
     <t>Den rikedom som finns i det vi ärvt är oftast oersättlig. Material och genomarbetat hantverk från tidigare tider, lager av mänsklig prägel och berättelser, en tätt vävd social struktur som skapar mening och tillhörighet, design av bestående kvalitet och karaktär, livfullt mångfacetterade användningsområden och en stark känsla för plats.
 Kvaliteter vi så ofta försöker återskapa är redan närvarande, i väntan på att tas om hand, anpassas och ges en ny användning.</t>
   </si>
@@ -307,20 +303,6 @@
 * **Genom tidig kartläggning** av material, struktur och rumslig logik, utvärderas olika alternativ för återanvändning eller anpassning.
 * **Denna iterativa process** bygger en grund för informerade beslutsfattanden, där miljömässiga, sociala och arkitektoniska kvaliteter integreras från start.
 * **Det är inte en designfas**, utan en iterativ process av att utforska scenarier för bästa möjliga väg framåt.</t>
-  </si>
-  <si>
-    <t>The starting point is observation and evaluation. AAA believes the concrete reality, the materials, structure and layers of use, must be understood to unlock the potential of a building or place.
-* **Through early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
-* **This iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
-* **It is not a phase of design**, but an iterative process of exploring scenarios of the best way forward.</t>
-  </si>
-  <si>
-    <t>AAA has long worked with these challenges, developing methods that combine design intelligence, strategic decision-making and architectural experience.
-* In Växjö AAA received first prize for a reuse strategy of Växjö hospital. 
-* Together with the property developer Riksbyggen, AAA is currently exploring adaptive reuse alternatives of an office and workshop building in Stockholm working with *generative AI*.
-* Recurrently AAA is invited to speak on the evolving practices and sustainable strategies for urban planning.
-Each building and place presents its own unique case; methods must be tailored to its specific needs and potential. 
-**Navigating this intersection of economy and ecology, culture and technology, is AAA’s expertise.**</t>
   </si>
   <si>
     <t>AAA har länge arbetat med dessa utmaningar och utvecklat metoder som kombinerar designintelligens, strategiskt beslutsfattande och arkitektonisk erfarenhet.
@@ -519,10 +501,6 @@
 </t>
   </si>
   <si>
-    <t>Through an adaptive approach AAA responds to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have challenges us to be creative and put to best use of our economic and ecological resources.
-We are building for a new future, with the beautiful legacy that came before us.</t>
-  </si>
-  <si>
     <t>Before founding AAA in 2024, Henrik Almquist gained experience at Arrhov Frick in Stockholm, Studio Muoto and Sou Fujimoto in Paris. He has carried out projects ranging from in-situ dialogues and early design proposals to overseeing construction. Henrik teaches at Lund University, where he directs the master studio Act of Altering on preservation and renovation. He is an active voice in the public dialogue on the existing built environment and sustainability.</t>
   </si>
   <si>
@@ -530,6 +508,28 @@
 In 2023 AAA won the competition for a reuse and development strategy for the Växjö hospital area. Current work includes renovation projects and an early phase study with Riksbyggen. Research funded by ARQ develops methods to identify existing values and adaptation potential in buildings.
 Phone: [+46793513461](tel:+46793513461)
 Email: contact@a-a-a.se</t>
+  </si>
+  <si>
+    <t>The richness inherited is often irreplaceable. Materials and elaborate craftsmanship from past times, layers of human touch and stories, a tightly woven social fabric creating purpose and a sense of belonging, design of enduring quality and character, vibrant diverse uses and a strong sense of place.
+Qualities we so often try to recreate are already present, waiting to be cared for, adapted and brought into new use.</t>
+  </si>
+  <si>
+    <t>Through an adaptive approach AAA responds to the rapid changes in how we plan, build and live as a society. A building can stand for more than 100 years, while a use of space can change quickly. Caring for the environment and the buildings we already have, challenges us to be creative and put to the best use of our economic and ecological resources.
+We are building for a new future, with the beautiful legacy that came before us.</t>
+  </si>
+  <si>
+    <t>The starting point is observation and evaluation. AAA believes that the concrete reality, the materials, structure and layers of use, must be understood to unlock the potential of a building or place.
+* **Through early-stage mapping** of materials, structure, and spatial logic, different options for reuse or adaptation are evaluated. 
+* **This iterative process** builds a foundation for informed decision-making, where environmental, social, and architectural qualities are integrated from the start.
+* **It is not a phase of design**, but an iterative process of exploring scenarios for the best way forward.</t>
+  </si>
+  <si>
+    <t>AAA has long worked with these challenges, developing methods that combine design intelligence, strategic decision-making and architectural experience.
+* In Växjö AAA received first prize for a reuse strategy of Växjö hospital. 
+* Together with the property developer Riksbyggen, AAA is currently exploring adaptive reuse alternatives of an office and workshop building in Stockholm working with generative AI.
+* AAA is regularly invited to speak on the evolving practices and sustainable strategies for urban planning.
+Each building and place presents its unique case; methods must be tailored to its specific needs and potential. 
+**Navigating this intersection of economy and ecology, culture and technology is AAA’s expertise.**</t>
   </si>
 </sst>
 </file>
@@ -3593,7 +3593,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>63</v>
@@ -6189,7 +6189,7 @@
         <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -6212,16 +6212,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>54</v>
@@ -6230,7 +6230,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="2">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="I2" s="2">
         <v>2</v>
@@ -6247,10 +6247,10 @@
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>43</v>
@@ -6259,7 +6259,7 @@
         <v>17</v>
       </c>
       <c r="H3" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I3" s="2">
         <v>2</v>
@@ -6276,10 +6276,10 @@
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>55</v>
@@ -6288,10 +6288,10 @@
         <v>26</v>
       </c>
       <c r="H4" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
@@ -6305,10 +6305,10 @@
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>56</v>
@@ -6317,10 +6317,10 @@
         <v>27</v>
       </c>
       <c r="H5" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
@@ -6334,10 +6334,10 @@
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>61</v>
@@ -6346,10 +6346,10 @@
         <v>28</v>
       </c>
       <c r="H6" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
@@ -6363,10 +6363,10 @@
         <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>57</v>
@@ -6375,10 +6375,10 @@
         <v>31</v>
       </c>
       <c r="H7" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I7" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="145" x14ac:dyDescent="0.35">
@@ -6392,10 +6392,10 @@
         <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>62</v>
@@ -6404,10 +6404,10 @@
         <v>34</v>
       </c>
       <c r="H8" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="174" x14ac:dyDescent="0.35">
@@ -6421,10 +6421,10 @@
         <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>58</v>
@@ -6433,27 +6433,27 @@
         <v>37</v>
       </c>
       <c r="H9" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>59</v>
@@ -6465,7 +6465,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -9371,13 +9371,13 @@
         <v>44</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -9394,13 +9394,13 @@
         <v>45</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -9417,10 +9417,10 @@
         <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>47</v>
@@ -11847,10 +11847,10 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>66</v>
@@ -11862,19 +11862,19 @@
         <v>68</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>69</v>
@@ -11900,19 +11900,19 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2">
@@ -11921,17 +11921,17 @@
     </row>
     <row r="6" spans="1:8" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -11941,22 +11941,22 @@
     </row>
     <row r="7" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2">
@@ -12015,11 +12015,11 @@
     </row>
     <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F4C562-61AC-4236-818E-7DC6348EB5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3D0827-C9CC-455A-AD93-C33BE3587EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" activeTab="5" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Architecture" sheetId="1" r:id="rId3"/>
     <sheet name="Adaptive" sheetId="2" r:id="rId4"/>
     <sheet name="Agency" sheetId="4" r:id="rId5"/>
+    <sheet name="p- could" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="139">
   <si>
     <t>Index</t>
   </si>
@@ -531,6 +532,59 @@
 Each building and place presents its unique case; methods must be tailored to its specific needs and potential. 
 **Navigating this intersection of economy and ecology, culture and technology is AAA’s expertise.**</t>
   </si>
+  <si>
+    <t>AAA021</t>
+  </si>
+  <si>
+    <t>Could You Live Here?</t>
+  </si>
+  <si>
+    <t>Explores the latent potential of buildings that are no longer considered viable within current models and practices. Through an inventory, generative AI, plans, regulations, and evaluations of cost and climate impact, the project develops feasible scenarios within existing space and structure. A deeper case study of Instrumentet 17 in Örnsberg investigates how a 1950s and 1960s building once planned for demolition could support new ways of living and working. Led by Henrik Almquist.</t>
+  </si>
+  <si>
+    <t>AAA021/AAA021_Could_You_Live_Here_(q)_01.png,
+AAA021/010.png,
+AAA021/006.png</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Category: Research and method development</t>
+  </si>
+  <si>
+    <t>/project/could-you-live-here-(q)</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Img</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Instrumentet 17</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
+    <t>s013</t>
+  </si>
+  <si>
+    <t>s230</t>
+  </si>
+  <si>
+    <t>s330</t>
+  </si>
 </sst>
 </file>
 
@@ -6170,15 +6224,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753E04D3-4F26-42C1-99ED-EFD612322389}">
-  <dimension ref="A1:I268"/>
+  <dimension ref="A1:J269"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="6" width="40.6328125" customWidth="1"/>
     <col min="7" max="7" width="47.6328125" customWidth="1"/>
     <col min="8" max="9" width="10.6328125" customWidth="1"/>
+    <col min="10" max="10" width="38.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6206,8 +6261,11 @@
       <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="J1" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -6236,114 +6294,115 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="I3" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="145" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="H4" s="2">
         <v>0.1</v>
       </c>
       <c r="I4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="188.5" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2">
         <v>0.1</v>
       </c>
       <c r="I5" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="2">
         <v>0.1</v>
@@ -6352,27 +6411,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H7" s="2">
         <v>0.1</v>
@@ -6381,56 +6440,56 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="145" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2">
         <v>0.1</v>
       </c>
       <c r="I8" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="174" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2">
         <v>0.1</v>
@@ -6439,47 +6498,65 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="174" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I10" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -6490,7 +6567,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -6501,7 +6578,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -6512,7 +6589,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -6523,7 +6600,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -9305,6 +9382,17 @@
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="2"/>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A269" s="2"/>
+      <c r="B269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+      <c r="E269" s="2"/>
+      <c r="F269" s="2"/>
+      <c r="G269" s="2"/>
+      <c r="H269" s="2"/>
+      <c r="I269" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14601,4 +14689,83 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCDA52FD-2EFA-4CEB-9405-A77E85ACCAC2}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="6" width="25.6328125" customWidth="1"/>
+    <col min="7" max="11" width="15.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3D0827-C9CC-455A-AD93-C33BE3587EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C627A4-67F4-485B-BE60-16DC2CC5F0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" activeTab="5" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="7" r:id="rId1"/>
@@ -539,18 +539,7 @@
     <t>Could You Live Here?</t>
   </si>
   <si>
-    <t>Explores the latent potential of buildings that are no longer considered viable within current models and practices. Through an inventory, generative AI, plans, regulations, and evaluations of cost and climate impact, the project develops feasible scenarios within existing space and structure. A deeper case study of Instrumentet 17 in Örnsberg investigates how a 1950s and 1960s building once planned for demolition could support new ways of living and working. Led by Henrik Almquist.</t>
-  </si>
-  <si>
-    <t>AAA021/AAA021_Could_You_Live_Here_(q)_01.png,
-AAA021/010.png,
-AAA021/006.png</t>
-  </si>
-  <si>
     <t>Link</t>
-  </si>
-  <si>
-    <t>Category: Research and method development</t>
   </si>
   <si>
     <t>/project/could-you-live-here-(q)</t>
@@ -584,6 +573,21 @@
   </si>
   <si>
     <t>s330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category: Research and development
+Year: 2026
+Client/funding: Riksbyggen, Tengbom, Konstakademin
+Use: Renovation to housing
+</t>
+  </si>
+  <si>
+    <t>Explores the renovation potential of existing buildings through new uses and adapted programmes. Combining building inventory, generative AI, planning and regulatory analysis, and assessments of economy and climate impact, the project develops and compares feasible scenarios within existing structures. A detailed case study of Instrumentet 17 in Örnsberg investigates how a 1950s and 1960s building can accommodate new ways of living and working.</t>
+  </si>
+  <si>
+    <t>AAA021/in01_t08_00339_.png,
+AAA021/AAA021_Could_You_Live_Here_(q)_01.png,
+AAA021/in01_t08_00196_.png</t>
   </si>
 </sst>
 </file>
@@ -6262,7 +6266,7 @@
         <v>15</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
@@ -6305,14 +6309,14 @@
         <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -6321,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
@@ -14702,22 +14706,22 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -14732,37 +14736,37 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" t="s">
         <v>132</v>
       </c>
-      <c r="B3" t="s">
-        <v>135</v>
-      </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Input text AAA.xlsx
+++ b/Input text AAA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\henrikalmquist.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C627A4-67F4-485B-BE60-16DC2CC5F0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F6E7C8-3955-4466-9B9B-2A5E4FEC3B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" activeTab="2" xr2:uid="{75645F56-5FAC-422B-9288-0CDC3C429DEC}"/>
   </bookViews>
@@ -575,19 +575,21 @@
     <t>s330</t>
   </si>
   <si>
+    <t>Explores the renovation potential of existing buildings through new uses and adapted programmes. Combining building inventory, generative AI, planning and regulatory analysis, and assessments of economy and climate impact, the project develops and compares feasible scenarios within existing structures. A detailed case study of Instrumentet 17 in Örnsberg investigates how a 1950s and 1960s building can accommodate new ways of living and working.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Category: Research and development
 Year: 2026
-Client/funding: Riksbyggen, Tengbom, Konstakademin
+Client/fund.: Riksbyggen, Tengbom, AA Palmérs
 Use: Renovation to housing
 </t>
   </si>
   <si>
-    <t>Explores the renovation potential of existing buildings through new uses and adapted programmes. Combining building inventory, generative AI, planning and regulatory analysis, and assessments of economy and climate impact, the project develops and compares feasible scenarios within existing structures. A detailed case study of Instrumentet 17 in Örnsberg investigates how a 1950s and 1960s building can accommodate new ways of living and working.</t>
-  </si>
-  <si>
     <t>AAA021/in01_t08_00339_.png,
 AAA021/AAA021_Could_You_Live_Here_(q)_01.png,
-AAA021/in01_t08_00196_.png</t>
+AAA021/in01_t08_00196_.png,
+AAA021/20250918_131927.jpg,
+AAA021/_MG_6191.jpg</t>
   </si>
 </sst>
 </file>
@@ -6309,10 +6311,10 @@
         <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
